--- a/UVA_PI_master_list.xlsx
+++ b/UVA_PI_master_list.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4885" uniqueCount="2483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5281" uniqueCount="2832">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -6302,1222 +6302,2269 @@
     <t xml:space="preserve">Patricio</t>
   </si>
   <si>
+    <t xml:space="preserve">University of Virginia, Dept. of Pediatrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Pediatrics job postings (AAMC) recruit a lab specialist to support Dr. Patricio Ray's research; postings undated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careerconnect.aamc.org/job/laboratory-specialist-senior-staff-wage/85770962/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redemann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefanie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Physiology &amp; Biophysics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Redemann Lab site on med.virginia.edu; joined UVA Physiology in 2018, no evidence of departure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/redemann-lab/?p=1374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aaron@dataclassroom.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataclassroom.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reidenbach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reidenbach@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Environmental Sciences (as of 2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only found a Jan 2023 UVA EVSC news item honoring Matt Reidenbach; no 2025-2026 evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://evsc.as.virginia.edu/news/story/7206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reidy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montefiore / Albert Einstein College of Medicine (Bronx, NY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kimberly J. Reidy is Chief of Pediatric Nephrology at Montefiore and faculty at Einstein; Multi-PI co-lead elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://montefioreeinstein.org/profiles/1760652556/kimberly-j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pr6e@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Materials Science and Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current UVA Engineering faculty page lists Petra Reinke as professor of MSE, email pr6e@virginia.edu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/petra-reinke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ribic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Psychology/Neuroscience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM faculty listing and Ribic NeuroLab (Gilmer Hall) show her as Assistant Professor of Neuroscience at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/ar5pt/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Center for Public Health Genomics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty listing shows Stephen S. Rich, Harrison Professor of Public Health Sciences (director emeritus of CPHG).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/ssr4n/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ritterband</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Psychiatry &amp; Neurobehavioral Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty listing shows Ritterband as professor and director of the Center for Behavioral Health and Technology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/lr5b/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberson-Nay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roxann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM faculty listing shows Roberson-Nay as Professor of Psychiatry; earlier career at VCU (through at least 2019).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/kac8uu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodriguez Lozano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health, Cardiology (per undated AHA article)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHA Eastern States article describes her leading UVA's Women's Heart Care Program; undated, no UVA-domain profile found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://easternstates.heart.org/?p=18400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rohde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gustavo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Biomedical Engineering / ECE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM faculty listing shows Rohde as Professor of BME; elected AIMBE Fellow in 2025 as UVA faculty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/gr2z/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jsr2pz@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Mathematics (as of 2018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018 UVA Math Bulletin reports hiring James Rolf for calculus reform; no 2025-2026 evidence found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://math.virginia.edu/2018/12/bulletin/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronfeldt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ronfeldt@umich.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosenthal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No UVA-linked Eric Rosenthal found; results show others (e.g., Eric S. Rosenthal at Mass General), likely a Multi-PI elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.massgeneral.org/vascular-center/doctors/18529/eric-rosenthal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health / University of Virginia School of Medicine, Nephrology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current uvahealth.com provider profile for Mitchell H. Rosner, MD; leads UVA Health as EVP for health affairs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uvahealth.com/providers/Mitchell-Rosner-1164591707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathryn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Florida, Clinical and Health Psychology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathryn M. Ross is Associate Professor &amp; Associate Chair for Research at UF; no UVA link found (Multi-PI co-lead elsewhere).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cicmd.center.ufl.edu/profile/ross-kathryn/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches found no Fernando Ruiz linked to UVA; common name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sdr2n@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Orthopaedic Surgery/Engineering (as of 2018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only a 2018 UVA Today faculty spotlight on Prof. Shawn Russell found; NSF record has virginia.edu email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news.virginia.edu/video/faculty-spotlight-professor-shawn-russell?page=12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutkowski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melanie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia (as of 2019); possibly Texas A&amp;M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA evidence dates to 2019, but a Rutkowski Lab page on research.tamhsc.edu (Texas A&amp;M) suggests a possible move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://research.tamhsc.edu/rutkowskilab/group/about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araceli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches found no Araceli Santiago linked to UVA; only unrelated namesakes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saucerman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current UVA Engineering faculty profile; AIMBE fellow 2023, cardiac systems biology lab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/jeffrey-saucerman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Michigan (Molecular &amp; Integrative Physiology)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Former UVA Cang lab postdoc; became Assistant Professor at U Michigan Jan 2023.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ion.uoregon.edu/ionsem-230502-elise-savier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kschiro@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No search results found for this name; has virginia.edu email on NSF grant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scialla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sept 2025 UVA nephrology update names her director of Nephrology Clinical Research Center; UVA Health provider profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.uvahealth.com/providers/Julia-Scialla-1780730036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Biomedical Engineering / nanoSTAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joined UVA 2024 from Northwestern as nanoSTAR director; later UVA giving stories show him at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news.med.virginia.edu/featured/evan-scott-phd-appointed-to-direct-uva-nanostar/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sedigh-Sarvestani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madineh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cornell University (Neurobiology and Behavior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs Sarvestani lab at Cornell; Multi-PI co-lead at another institution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nature.com/naturecareers/apply/12848945/research-technician-sarvestani-lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sequeira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zbp2sm@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scholars profile lists her as Assistant Professor of Psychology at UVA; virginia.edu email on grant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://scholars.org/scholar/stefanie-l-sequeira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sequeira-Lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Luisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Pediatrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health researcher highlight: Harrison Distinguished Professor of Pediatrics, renin research; 2024 lab output.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.uvahealth.com/healthy-practice/researcher-highlight-sequeira-lopez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Psychiatry and Neurobehavioral Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current med.virginia.edu faculty listing as Associate Professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/kms8nr/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shafiee-Jood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ms2dm@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering (Civil &amp; Environmental / Systems &amp; Information Engineering)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SIE people listing shows him as Research Assistant Professor; joined UVA in 2020; virginia.edu email on grant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/department/systems-and-information-engineering/people?page=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common name; two searches found no Ajay Sharma at UVA (one namesake at Univ. of Georgia); likely Multi-PI elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rahul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA nephrology pages list Rahul Sharma PhD, Associate Professor; Virginia Catalyst grant; no evidence of departure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/nephrology/our-division/awards-honors-scientific-contributions/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaughnessy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mshaugh@bu.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bu.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheffield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Genome Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April 2025 UVA Genome Sciences news on his new genomic data standard; Associate Professor at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/genome-sciences/2025/04/03/new-tool-streamlines-genomic-research-accelerating-biomedical-breakthroughs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cong@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current UVA Engineering faculty page lists him as Associate Professor of ECE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/cong-shen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haiying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hs6ms@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering faculty profile lists her in Computer Science (latest dated item 2022 ACM honor).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/haiying-shen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shepherd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Center for Health Humanities and Ethics / Law</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA biomedical ethics faculty page and 2024 vita show her as Wallenborn Professor at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/biomedical-ethics/people/lois-shepherd/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northeastern University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Shepherd is an assistant professor at Northeastern (engineering + rehabilitation), joined 2022; Multi-PI co-lead, not UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://coe.northeastern.edu/people/shepherd-max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sherriff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mss2x@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty page plus SIGCSE 2026 profile list him as Professor of CS at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/mark-sherriff-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sherwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Nursing profile and 2024 new-faculty news: moved from Pitt to UVA in 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheybani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natasha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April 2025 news on her $5.5M DoD grant as UVA BME assistant professor; UVA lab page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.news-medical.net/news/20250411/UVA-researcher-wins-major-grant-to-revolutionize-breast-cancer-treatment.aspx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheynkman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Molecular Physiology and Biological Physics (as of 2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only a 2024 UVA CVRC seminar listing (as Assistant Professor, MPBP) found; no 2025-26 evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cvrc.virginia.edu/seminars/2024-03-11/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yingtang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One search found no Yingtang Shi profile anywhere; Multi-PI, may be at another institution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM faculty listing page for Yun Shim (yss6n), updated June 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/yss6n/yss6n-2/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jung-Bum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Neuroscience primary faculty page lists him as Professor, Auditory Neurobiology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/neuroscience/faculty/primary-faculty/jung-bum-shin-ph-d/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Surgery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb 2025 UVA SOM research news profiles Thomas Shin, MD, PhD, bariatric surgeon-scientist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news.med.virginia.edu/category/research/page/15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shukla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nikhil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ns6pf@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Electrical and Computer Engineering / MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering pages show him as associate professor leading the Computing Hardware Research Lab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/labs-groups/computing-hardware-research-lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sidiropoulos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nikolaos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nikos@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IEEE SPS profile lists him as Louis T. Rader Professor of ECE at UVA; virginia.edu email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://signalprocessingsociety.org/index.php/tags/nikolaos-sidiropoulos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siegrist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches found no Mary Siegrist at UVA or elsewhere; Multi-PI may be at another institution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Department of Biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA expand.virginia.edu NRT profile lists her in the Biology Department.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://expand.virginia.edu/people/sarah-siegrist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silbergleit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Michigan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professor of emergency medicine at the University of Michigan, SIREN network CCC PI; Multi-PI co-lead, not at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.uofmhealth.org/profile/1045/robert-silbergleit-md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meenesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mrsingh@uic.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uic.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siracusa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutgers Biomedical and Health Sciences (Newark)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontiers Loop profile lists Mark C. Siracusa at Rutgers; Multi-PI co-lead elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://loop.frontiersin.org/people/328078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skadron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skadron@cs.virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Douglas Forsyth Professor of CS at UVA; current UVA Engineering news and CRISP pages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/news-events/news/uva-engineerings-skadron-elected-virginia-academy-science-engineering-and-medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slawski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebh3ep@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia, Department of Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA A&amp;S faculty profile as associate professor of statistics; teaching listed through Spring 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://as.virginia.edu/faculty-profile/martin-slawski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slingluff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health / School of Medicine, Surgery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health provider page; May 2025 UVA Cancer Center news names him a consortium representative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uvahealth.com/providers/craig-slingluff-1477687283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Biochemistry and Molecular Genetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current med.virginia.edu faculty listing for Jeffrey S. Smith, Professor of BMG (yeast silencing/aging).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/jss5y/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search found no Lora Smith at UVA, only similarly named people elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">possibly UVA Health Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only a Healthline listing for a Dr. Scott Smith at UVA Health Infectious Diseases Clinic; common name, unverified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://care.healthline.com/find-care/provider/dr-scott-smith-1538216346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soffa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soffa@cs.virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia (emerita)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering faculty page lists her as Owen R. Cheatham Professor of Sciences Emerita; retired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.engineering.virginia.edu/faculty/mary-lou-soffa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jgs8e@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expert directory lists him as associate professor of quantitative methods at UVA SEHD; NSF email is virginia.edu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.newswise.com/users/expert-list-expertise/59990_Standardized+Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somerville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches (pediatrics, cystic fibrosis) returned no page naming Lindsay Somerville at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyun-Seob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hsong5@unl.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonkusare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swapnil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Molecular Physiology and Biological Physics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named a UVA Pinn Scholar in July 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/physiology-biophysics/2025/07/03/swapnil-sonkusare-appointed-as-a-pinn-scholar-congratulations/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sontheimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Neuroscience (Chair)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Neuroscience faculty page lists him as Professor and Chair; 2025 prize lists UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/neuroscience/faculty/primary-faculty/harald-sontheimer-ph-d/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spencer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brady</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Microbiology, Immunology, and Cancer Biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sept 2024 UVA SOM news reports assistant professor Brady Spencer got an NIH K22; no 2025-26 evidence found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news.med.virginia.edu/?p=32965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sperling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Pulmonary and Critical Care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA pulmonary faculty page; named UVA COWIMS Honoree of the Month in June 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/pulmonary/bench-research/anne-i-sperling-phd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiliotis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Virginia School of Medicine, Cell Biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joined UVA Cell Biology from Drexel in 2024; July 2025 UVA news reports a NIGMS grant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/cell-biology/2024/02/15/uva-cell-biology-welcomes-dr-elias-spiliotis/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cliff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA chemistry course listings through Spring 2025 and his UVA group site carries Oct 2025 lab news.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uva.theopenscholar.com/cliff-stains/links-new</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marilyne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mstains@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Chemistry people page lists her as professor (joined 2019, full professor 2022).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://chemistry.as.dev.artscid9.virginia.edu/people/marilyne-stains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mircea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mircea@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA ECE (likely)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Math Genealogy shows UVA PhD students (2007, 2015); no current profile surfaced, though grant email is virginia.edu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mathgenealogy.org/id.php?id=133412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches found no Amber Steen at UVA or elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stukenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P. Todd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Biochemistry &amp; Molecular Genetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM news from 2022-2023 shows him as professor; no 2025+ evidence found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/bmg/2023/02/02/dr-david-wotton-and-dr-todd-stukenberg-awarded-the-2022-uva-research-collaboration-award/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stupp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northwestern University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board of Trustees Professor at Northwestern; no UVA affiliation (Multi-PI co-lead elsewhere).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://chemistry.northwestern.edu/people/core-faculty/profiles/samuel-stupp.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sturek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine (Pulmonary/Critical Care)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 2025 UVA SOM news: associate professor, new $4M NHLBI grant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news.med.virginia.edu/?p=49304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brynne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Pediatrics/Neonatology (Center for Advanced Medical Analytics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty page lists her as associate professor of pediatrics and CAMA director.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/advanced-medical-analytics/our-people/brynne-sullivan-md-msc/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rush University Medical Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely D. Rick Sumner, professor and chair at Rush per April 2026 CV; Multi-PI co-lead elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rushu.rush.edu/sites/default/files/2026-04/SumnerCV-04-2026.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Infectious Diseases / Carter Immunology Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty listing and 2026 Carter Center news (NIH grant April 2026) show him at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/js6re/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shengyi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty listing and 2025 UVA Cancer Center news show her as associate professor of pharmacology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/cancer-research/about-us/news/news-archive-2025/cancer-center-research-faculty-welcomes-shengyi-iris-sun-phd/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dzv7sg@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept of Mechanical and Aerospace Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA engineering directory lists Ye (Sarah) Sun as associate professor in MAE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/s?page=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yixin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ys3kz@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty page and CV (Spring 2026 courses) show her as CS assistant professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/yixin-sun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sutherland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search found no Ann Sutherland at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suzuki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas A&amp;M University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only matching Masako Suzuki is an assistant professor at Texas A&amp;M (adjunct at Einstein); likely Multi-PI co-lead elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://loop.frontiersin.org/people/1095956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only an old undated Wichita State notice lists him as UVA ECE assistant professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.wichita.edu/about/wsunews/archive/index.php?cnid=4779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swenor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonnielin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johns Hopkins University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of JHU Disability Health Research Center; no UVA link (Multi-PI co-lead elsewhere).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://nursing.jhu.edu/faculty-research/faculty/directory/bonnielin-swenor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lukas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Molecular Physiology &amp; Biological Physics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM faculty listing: Harrison Professor, Director of Center for Membrane and Cell Physiology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/lkt2e/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jctan.astro@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Astronomy faculty &amp; senior research staff directory lists him as Research Professor (VITA).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://astronomy.as.virginia.edu/faculty-senior-research-staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shangming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No search result for Shangming Tang at UVA or elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tengteng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toni.Tang@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unclear (UVA email on grant; Union College page found)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undated Union College page lists a Tengteng Tang as ME assistant professor; no UVA page found despite virginia.edu grant email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.union.edu/me/faculty-staff/tengteng-tang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taniuchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Medicine, Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sept 2023 UVA SOM news lists her as associate professor; no 2025+ evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news.med.virginia.edu/category/faculty/page/31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teachman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bethany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Psychology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA TYDE page and Newswise profile show Commonwealth Professor and Director of Clinical Training at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tyde.virginia.edu/?p=305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teague</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Pediatrics (Respiratory Medicine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA CHRC key-investigator page lists W. Gerald Teague, Ivy Foundation Distinguished Professor of Pediatrics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/chrc/key-investigators/w-gerald-teague-md/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mt2yq@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches found no Mariana Teles at UVA; grant email mt2yq@virginia.edu is a UVA computing ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tepe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jetze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Chemistry / UVA Cancer Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joined UVA Chemistry Jan 2024 as Cancer Center Director of Drug Discovery (moved from Michigan State).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/cancer-research/about-us/news/news-archive-2024/jetze-tepe-phd-joins-cancer-center-research-faculty/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therrien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wjt2c@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA education directory lists William J. Therrien as Thomas G. Jewell Professor of Education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://education.virginia.edu/about/directory/william-j-therrien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elt@tamu.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tamu.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mpt9g@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA (Professor, Chemical Engineering)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public payroll data shows Michael Timko as UVA Professor with a 2026 salary entry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://openpayrolls.com/employee/michael-timko-4164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA CVRC and med.virginia.edu profiles list him as Associate Professor of Medicine; he moved from VCU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cvrc.virginia.edu/faculty-individual/?Id=167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ygn5rz@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Department of Astronomy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Astronomy faculty listing shows Paul Torrey as Associate Professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ming-Feng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA med faculty listing shows him as Associate Professor (lab at tsaislab.org); he moved from Colorado after 2023.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/vmf6uw/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsihlis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Departments of Surgery and Biomedical Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kibbe-Tsihlis lab page lists Nick D. Tsihlis as Professor of Research and co-PI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/kibbe-tsihlis-lab/team-members/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Chair of Surgery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Surgery faculty listing shows Allan Tsung as Professor and Chair, appointed in 2022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/surgery/faculty-listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tzounopoulos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thanos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Pittsburgh (Otolaryngology)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pitt pages list him as Professor and Director of the Pittsburgh Hearing Research Center; he is a Multi-PI co-lead at another institution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cnup.pitt.edu/people/thanos-tzounopoulos-phd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valdez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Public Health Sciences / Engineering Systems and Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering faculty directory lists Rupa S. Valdez; UVA Health news shows her as Associate Professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van Berlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johannes (Jop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Minnesota (Lillehei Heart Institute / Stem Cell Institute)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search results place Jop van Berlo at the University of Minnesota and show no UVA link; he is a Multi-PI co-lead elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://app.jove.com/author/42969/jop-h-van-berlo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van Horn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Data Science and Department of Psychology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Data Science profile and 2025 OHBM award news show him at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://datascience.virginia.edu/news/john-van-horn-recognized-ohbm-2025-education-neuroimaging-award</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vassallo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayo Clinic, Rochester MN (Pulmonology)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayo Clinic biography lists Robert Vassallo as a pulmonologist in Rochester; no UVA listing found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mayoclinic.org/biographies/vassallo-robert-m-d/bio-20054445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vecchiarello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qzv7pp@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Department of Chemical Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA ChemE directory lists Nick Vecchiarello as Assistant Professor; UVA news reports his NSF CAREER award.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/department/chemical-engineering/people?page=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venkat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">av6ds@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering pages list Ashish Venkat as William Wulf Career Enhancement Associate Professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/department/computer-science/people?page=7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Department of Chemistry (Chair)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Jill Venton is Thomas Jefferson Professor and Chair of UVA Chemistry per the UVA lab site and CV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uva.theopenscholar.com/venton-group/jill-venton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Gaudecker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indiana University School of Nursing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflicting: UVA Nursing page lists her; Indiana University news from Sept-Oct 2025 still shows her at IU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://nursing.iu.edu/directory/profiles/von-gaudecker-jane.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vucelja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marija</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvucelja@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Department of Physics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theCourseForum shows her teaching UVA physics courses through Fall 2025 with a virginia.edu email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thecourseforum.com/instructor/6572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vullikanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact PI, PI, Co-PI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asv9v@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Computer Science and Biocomplexity Institute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering profile plus 2025 UVA award news show him as Professor at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/anil-vullikanti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Berne Cardiovascular Research Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA news and CVRC pages list him as Lockhart B. McGuire Professor of Medicine directing the Hematovascular Biology Center, with recent NIH grant news.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cvrc.virginia.edu/tag/walsh/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jingming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdw9qv@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Department of Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current UVA Statistics people page lists her as Assistant Professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://statistics.as.virginia.edu/people/jingming-wang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lixin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches found no UVA-linked Lixin Wang, only same-name researchers in China.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tianhao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tianhao@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Computer Science / School of Data Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA TYDE team page and CS news list him as an assistant professor with an NSF CAREER award.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tyde.virginia.edu/team/tianhao-wang/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weiqiang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ww9c@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Mathematics (likely)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Math Genealogy shows UVA PhD students through 2024, but no 2025-2026 UVA profile found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mathgenealogy.org/id.php?id=65146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weaver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only an undated payroll aggregator lists a UVA Assistant Professor named Tyler Weaver; no department found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://openpayrolls.com/employee/anda-webb-4164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine (Wenker Lab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Wenker Lab news shows activity through Feb 2026, including a UVA Research in Motion talk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/wenker-lab/lab-news/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Department of Molecular Physiology and Biophysics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA MPBP announcement says he joined as an assistant professor in Sept 2024; no sign he left.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/physiology-biophysics/2024/10/09/welcome-two-new-mpbp-faculty/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whittaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jew9t@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theCourseForum shows UVA Education courses taught by her through Spring 2026; she has a virginia.edu email.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://thecourseforum.com/instructor/4130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbwilson@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Architecture (likely Barbara Brown Wilson)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search shows a Barbara Brown Wilson in UVA urban planning (older pages); no 2025-2026 evidence found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://clarke.dickinson.edu/barbara-brown-wilson/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bw6xs@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Architecture, Urban and Environmental Planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current UVA Architecture profile lists Bev Wilson as a professor of urban and environmental planning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.arch.virginia.edu/people/bev-wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vma8ze@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Education directory lists her as an associate professor of mathematics education (formerly at NC State).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://education.virginia.edu/about/directory/jonee-wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winckler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bettina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Department of Cell Biology (Chair)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Aug 2026 UVA Health news item names her chair of the Department of Cell Biology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.uvahealth.com/news/leading-nervous-system-researcher-chair-uva-department-cell-biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiseman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb 2026 UVA SOM news covers her award and Research in Motion profile as an assistant professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news.med.virginia.edu/newsletter/2-19-26-issue/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two searches found no evidence of a Russell Witt at UVA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM faculty profile lists Matthew J. Wolf as Professor of Cardiovascular Medicine, with a lab in the Berne CVRC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/mjw5mc/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vcw2n@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search results describe her as Associate Professor of Research, Statistics and Evaluation at UVA SEHD; her email is a virginia.edu address.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.brookings.edu/author/vivian-wong/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adrienne.wood@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept of Psychology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA TYDE profile lists her as Assistant Professor of Psychology; she received a 2025 UW alumni award.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tyde.virginia.edu/team/adrienne-wood/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woodfolk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Asthma, Allergy and Immunology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA profile lists her as Professor of Medicine and MSTP Co-Director, with a 2025 publication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/asthma-allergy-immunology/research/judith-a-woodfolk-md-phd/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty listing shows Melanie I. Worley as Assistant Professor of Biology (Drosophila regeneration lab).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/rpc4ev/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worrall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health provider page and SOM profile list him as Professor of Neurology and Stroke Division Chief.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uvahealth.com/providers/bradford-worrall-1821167461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Biochemistry and Molecular Genetics (likely)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only UVA evidence found is a February 2023 award news item and an undated course listing; no 2025-2026 profile turned up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wythe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joshua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept of Cell Biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM profile lists him as Associate Professor of Cell and Developmental Biology; he moved from Baylor in 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/cell-biology/2024/04/26/uva-cell-biology-welcomes-dr-joshua-wythe/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jinghang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Molecular Physiology and Biological Physics (likely)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only evidence found is a June 2024 UVA Cancer Center news item about him joining as an assistant professor; nothing from 2025-2026 turned up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/cancer-research/about-us/news/news-archive-2024/jinghang-xie-phd-joins-cancer-center-research-faculty/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baoxing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The UVA Engineering faculty listing shows him as Associate Professor of Mechanical and Aerospace Engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kexin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept of Genome Sciences / Cancer Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January 2025 UVA Cancer Center news welcomes Kexin Xu as Professor of Genome Sciences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/cancer-research/about-us/news/news-archive-2025/gen-program-welcomes-kexin-xu-phd/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yadava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Pathology (Mahadevan lab), last seen 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramesh S. Yadava appears on UVA myotonic dystrophy papers up to 2021; no current profile was found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.uvahealth.com/news/potential-treatment-for-myotonic-muscular-dystrophy-identified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ky5t@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A November 2025 UVA 'Hoos in STEM' podcast features Kent Yagi as a UVA physics professor; his email ky5t matches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.audioscrape.com/podcast/hoos-in-stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guofen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept of Public Health Sciences, Biostatistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA PHS profile lists her as Professor of Biostatistics, and payroll records run through 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/phs/2017/09/07/yan-guofen-ph-d/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA SOM faculty listing shows him as an assistant professor (cryo-EM, cell stress); his lab opened in 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/wfw7nc/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">akz2wg@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wikipedia and DBLP list her as an associate professor of ECE at UVA; she has a recent-style UVA computing ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/Jing_Yang_(computer_engineer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xiyang@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA plant ecology lab page and DBLP list him as an associate professor in UVA Environmental Sciences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uva.theopenscholar.com/plant-ecology-lab/people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yaohua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept. of Genome Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Genome Sciences page (Aug 2024) and Frontiers profile list him as assistant professor at UVA; no sign he left.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/genome-sciences/tag/yaohua-yang/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zequan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept. of Surgery (TCV lab) / CVRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA faculty listing and TCV lab page list him as Associate Professor of Surgery; 2024 publications.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/zy6b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarboro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health, Cardiac Surgery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health provider profile shows her as chief of cardiac surgery; cites 2025 Newsweek award.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.uvahealth.com/providers/Leora-Yarboro-1437378643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xy3m@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search found no UVA page for Xu Yi; the only hits were namesakes in China.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept. of Public Health Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA PHS faculty profile lists her as Professor and director of a Cancer Center core; adjunct appointment at Virginia Tech.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/phs/2019/08/01/you-wen/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sy5jx@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Dept. of Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Statistics department profile lists her as assistant professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://statistics.as.virginia.edu/people/shan-yu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chongzhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact PI, Multi-PI, Co-PI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zang@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Center for Public Health Genomics / PHS / BME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA named him a 2024 Pinn Scholar (associate professor); multiple UVA appointments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/genome-sciences/2024/07/11/cphgs-chongzhi-zang-named-2024-pinn-scholar/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zawar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ifrah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health, Neurology (Epilepsy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health provider profile is live, and the 2025/2026 ANA speaker pages list her.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.uvahealth.com/providers/IFRAH-ZAWAR-1689076192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zebarjadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mz6g@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA ECE and Materials Science &amp; Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering faculty page lists her as professor; she leads the E-Snail lab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/mona-zebarjadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeichner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Health, Pediatric Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Children's provider profile lists him as professor of Pediatric ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://childrens.uvahealth.com/providers/steven-zeichner-1730275314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeidan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fadel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UC San Diego, Dept. of Anesthesiology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSD profile lists him as professor and director of the Pain Health and Mindfulness Lab; likely an external Multi-PI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://empathyandcompassion.ucsd.edu/about/people/profiles/fadel-zeidan-phd.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeitlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search found no Scott Zeitlin at UVA (likely the Scott Zeitlin in UVA Neuroscience/Huntington disease, but not verified).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aidong@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Computer Science / Data Science / BME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Data Science profile lists her as Linville Professor and interim CS chair.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://datascience.virginia.edu/people/aidong-zhang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miaomiao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mz8rr@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA ECE / Computer Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering faculty directory lists her as a joint ECE/CS faculty member.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/department/electrical-and-computer-engineering/faculty?page=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shangtong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shangtong.zhang.cs@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Engineering faculty page lists him as assistant professor in CS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.engineering.virginia.edu/faculty/shangtong-zhang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tianpeng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search found no UVA page for Tianpeng Zhang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xinyu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xyzhang@ucsd.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ucsd.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search found no UVA page for Hua Zhao; the only hits were namesakes at UMN, Brunel and Shandong.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown (likely external Multi-PI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search found no UVA Zhen Zhao; the only hits were namesakes at SDSU and elsewhere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhigilei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lz2n@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA, Materials Science and Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current UVA Engineering faculty profile lists him as Professor of MSE; leads the Computational Materials Group.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://engineering.virginia.edu/faculty/leonid-v-zhigilei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Pulmonary and Critical Care Medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Pulmonary faculty page lists Anny Xiaobo Zhou, PhD, as professor (moved from Harvard/BWH; hired March 2025 per payroll).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/pulmonary/anny-xiaobo-zhou-phd/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bicheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bicheng.zhou@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown (virginia.edu email on NSF award)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No web result found for Bicheng Zhou at UVA or elsewhere in two searches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Ophthalmology page lists Jenny H. Zhou, MD, PhD, as Associate Professor, January 2026 to present (previously Yale).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/ophthalmology/?p=6221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jingsong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Texas at Arlington, Kinesiology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only Jingsong Zhou found is Professor of Kinesiology at UT Arlington; likely an external Multi-PI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://zhounmdlab.uta.edu/?p=13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xbd7fb@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA (tenure-line associate professor, department not identified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 public payroll record shows Lin Zhou as UVA tenure-line associate professor hired July 2025; consistent with virginia.edu email on NSF award.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://openpayrolls.com/lin-zhou-178654445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hzhu2m@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Public Health Sciences (Biostatistics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA pages list Hong Zhu as Professor of Biostatistics and Faculty Director of the Biostatistics and Population Science Shared Resource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/bpssr/our-team-and-location/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohio State University, Department of Surgery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hua Zhu, PhD, is Professor of Surgery at Ohio State (MG53/muscle repair); no UVA link found, likely external Multi-PI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://medicine.osu.edu/find-a-researcher/hua-zhu-100003860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huiyuan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kkx8js@virginia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA, Chemistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA lab page lists her as Associate Professor of Chemistry since 2023.08 to present.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uva.theopenscholar.com/nano-energy-and-environmental-catalysis-lab/people/prof-huiyuan-zhu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qianqian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roswell Park Comprehensive Cancer Center, Biostatistics and Bioinformatics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qianqian Zhu, PhD, is Professor of Oncology at Roswell Park; no UVA link found, likely external Multi-PI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.roswellpark.org/qianqian-zhu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zimmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jochen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA named him Charles Slaughter Professor of Physiology, July 2024 to June 2029; HHMI honor news.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://med.virginia.edu/physiology-biophysics/2024/11/27/dr-jochen-zimmer-elected-to-the-charles-slaughter-professorship-in-physiology/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoellner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA reported in June 2026 on her new grant-funded sugary-drink study; Professor of Public Health Sciences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eurekalert.org/multimedia/895702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA School of Medicine, Microbiology, Immunology, and Cancer Biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVA Neuroscience Graduate Program and med.virginia.edu lab pages list him as professor in MIC (glioma research).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://neurograd.virginia.edu/hui-zong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not yet checked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redemann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefanie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aaron@dataclassroom.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataclassroom.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reidenbach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reidenbach@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reidy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reinke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pr6e@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ribic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ritterband</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberson-Nay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roxann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodriguez Lozano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patricia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rohde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustavo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jsr2pz@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronfeldt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ronfeldt@umich.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosenthal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kathryn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Russell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdr2n@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rutkowski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melanie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Araceli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saucerman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current UVA Engineering faculty profile; AIMBE fellow 2023, cardiac systems biology lab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://engineering.virginia.edu/faculty/jeffrey-saucerman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Michigan (Molecular &amp; Integrative Physiology)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Former UVA Cang lab postdoc; became Assistant Professor at U Michigan Jan 2023.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ion.uoregon.edu/ionsem-230502-elise-savier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kschiro@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No search results found for this name; has virginia.edu email on NSF grant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scialla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept 2025 UVA nephrology update names her director of Nephrology Clinical Research Center; UVA Health provider profile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.uvahealth.com/providers/Julia-Scialla-1780730036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Biomedical Engineering / nanoSTAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joined UVA 2024 from Northwestern as nanoSTAR director; later UVA giving stories show him at UVA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://news.med.virginia.edu/featured/evan-scott-phd-appointed-to-direct-uva-nanostar/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sedigh-Sarvestani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madineh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cornell University (Neurobiology and Behavior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runs Sarvestani lab at Cornell; Multi-PI co-lead at another institution.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.nature.com/naturecareers/apply/12848945/research-technician-sarvestani-lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sequeira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zbp2sm@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scholars profile lists her as Assistant Professor of Psychology at UVA; virginia.edu email on grant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://scholars.org/scholar/stefanie-l-sequeira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sequeira-Lopez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Luisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA School of Medicine, Pediatrics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Health researcher highlight: Harrison Distinguished Professor of Pediatrics, renin research; 2024 lab output.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.uvahealth.com/healthy-practice/researcher-highlight-sequeira-lopez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaffer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Psychiatry and Neurobehavioral Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current med.virginia.edu faculty listing as Associate Professor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/kms8nr/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shafiee-Jood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Majid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ms2dm@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rahul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA nephrology pages list Rahul Sharma PhD, Associate Professor; Virginia Catalyst grant; no evidence of departure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/nephrology/our-division/awards-honors-scientific-contributions/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaughnessy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mshaugh@bu.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bu.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheffield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cong@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haiying</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hs6ms@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shepherd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sherriff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mss2x@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sherwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheybani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natasha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheynkman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yingtang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jung-Bum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shukla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikhil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ns6pf@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sidiropoulos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikolaos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nikos@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siegrist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silbergleit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Singh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meenesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mrsingh@uic.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uic.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siracusa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skadron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skadron@cs.virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slawski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ebh3ep@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slingluff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soffa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soffa@cs.virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jgs8e@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somerville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyun-Seob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hsong5@unl.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonkusare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swapnil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sontheimer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spencer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brady</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sperling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spiliotis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cliff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marilyne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mstains@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mircea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mircea@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stukenberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P. Todd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stupp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sturek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brynne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA School of Medicine, Pediatrics/Neonatology (Center for Advanced Medical Analytics)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA faculty page lists her as associate professor of pediatrics and CAMA director.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/advanced-medical-analytics/our-people/brynne-sullivan-md-msc/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sumner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rush University Medical Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely D. Rick Sumner, professor and chair at Rush per April 2026 CV; Multi-PI co-lead elsewhere.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.rushu.rush.edu/sites/default/files/2026-04/SumnerCV-04-2026.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA School of Medicine, Infectious Diseases / Carter Immunology Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA faculty listing and 2026 Carter Center news (NIH grant April 2026) show him at UVA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/js6re/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shengyi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA faculty listing and 2025 UVA Cancer Center news show her as associate professor of pharmacology.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/cancer-research/about-us/news/news-archive-2025/cancer-center-research-faculty-welcomes-shengyi-iris-sun-phd/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dzv7sg@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Dept of Mechanical and Aerospace Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA engineering directory lists Ye (Sarah) Sun as associate professor in MAE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://engineering.virginia.edu/faculty/s?page=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yixin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ys3kz@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA faculty page and CV (Spring 2026 courses) show her as CS assistant professor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://engineering.virginia.edu/faculty/yixin-sun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sutherland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search found no Ann Sutherland at UVA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suzuki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas A&amp;M University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only matching Masako Suzuki is an assistant professor at Texas A&amp;M (adjunct at Einstein); likely Multi-PI co-lead elsewhere.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://loop.frontiersin.org/people/1095956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swenor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonnielin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lukas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jctan.astro@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shangming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tengteng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toni.Tang@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taniuchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teachman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bethany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teague</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mt2yq@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tepe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jetze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Therrien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wjt2c@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elt@tamu.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tamu.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mpt9g@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toldo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ygn5rz@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tsai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ming-Feng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tsihlis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tsung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tzounopoulos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thanos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valdez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rupa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Van Berlo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johannes (Jop)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Van Horn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vassallo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vecchiarello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qzv7pp@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venkat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">av6ds@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Von Gaudecker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vucelja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marija</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mvucelja@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vullikanti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact PI, PI, Co-PI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asv9v@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jingming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdw9qv@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lixin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tianhao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tianhao@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weiqiang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ww9c@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weaver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wenker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whitlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whittaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jew9t@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bbwilson@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beverly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bw6xs@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vma8ze@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Winckler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bettina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiseman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wolf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA SOM faculty profile lists Matthew J. Wolf as Professor of Cardiovascular Medicine, with a lab in the Berne CVRC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/mjw5mc/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vivian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vcw2n@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search results describe her as Associate Professor of Research, Statistics and Evaluation at UVA SEHD; her email is a virginia.edu address.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.brookings.edu/author/vivian-wong/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adrienne.wood@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Dept of Psychology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA TYDE profile lists her as Assistant Professor of Psychology; she received a 2025 UW alumni award.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://tyde.virginia.edu/team/adrienne-wood/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woodfolk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Judith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA School of Medicine, Asthma, Allergy and Immunology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA profile lists her as Professor of Medicine and MSTP Co-Director, with a 2025 publication.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/asthma-allergy-immunology/research/judith-a-woodfolk-md-phd/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA faculty listing shows Melanie I. Worley as Assistant Professor of Biology (Drosophila regeneration lab).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/faculty/faculty-listing/rpc4ev/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worrall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Health provider page and SOM profile list him as Professor of Neurology and Stroke Division Chief.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://uvahealth.com/providers/bradford-worrall-1821167461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Biochemistry and Molecular Genetics (likely)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The only UVA evidence found is a February 2023 award news item and an undated course listing; no 2025-2026 profile turned up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/bmg/2023/02/02/dr-david-wotton-and-dr-todd-stukenberg-awarded-the-2022-uva-research-collaboration-award/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wythe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joshua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Dept of Cell Biology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA SOM profile lists him as Associate Professor of Cell and Developmental Biology; he moved from Baylor in 2024.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/cell-biology/2024/04/26/uva-cell-biology-welcomes-dr-joshua-wythe/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jinghang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Molecular Physiology and Biological Physics (likely)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The only evidence found is a June 2024 UVA Cancer Center news item about him joining as an assistant professor; nothing from 2025-2026 turned up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/cancer-research/about-us/news/news-archive-2024/jinghang-xie-phd-joins-cancer-center-research-faculty/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baoxing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The UVA Engineering faculty listing shows him as Associate Professor of Mechanical and Aerospace Engineering.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://engineering.virginia.edu/faculty/x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kexin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Dept of Genome Sciences / Cancer Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">January 2025 UVA Cancer Center news welcomes Kexin Xu as Professor of Genome Sciences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/cancer-research/about-us/news/news-archive-2025/gen-program-welcomes-kexin-xu-phd/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yadava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Pathology (Mahadevan lab), last seen 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramesh S. Yadava appears on UVA myotonic dystrophy papers up to 2021; no current profile was found.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.uvahealth.com/news/potential-treatment-for-myotonic-muscular-dystrophy-identified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ky5t@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A November 2025 UVA 'Hoos in STEM' podcast features Kent Yagi as a UVA physics professor; his email ky5t matches.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.audioscrape.com/podcast/hoos-in-stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guofen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA Dept of Public Health Sciences, Biostatistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVA PHS profile lists her as Professor of Biostatistics, and payroll records run through 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://med.virginia.edu/phs/2017/09/07/yan-guofen-ph-d/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">akz2wg@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xiyang@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yaohua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zequan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarboro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xy3m@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sy5jx@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chongzhi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact PI, Multi-PI, Co-PI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zang@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zawar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ifrah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zebarjadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mz6g@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeichner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeidan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fadel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeitlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aidong@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miaomiao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mz8rr@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shangtong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shangtong.zhang.cs@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tianpeng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xinyu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xyzhang@ucsd.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ucsd.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhigilei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lz2n@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bicheng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bicheng.zhou@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jenny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jingsong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xbd7fb@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hzhu2m@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huiyuan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kkx8js@virginia.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qianqian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zimmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jochen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoellner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -7606,7 +8653,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7622,7 +8669,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -7635,12 +8682,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDEDED"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -7678,7 +8719,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7703,10 +8744,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7724,7 +8761,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7767,14 +8804,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEDEDED"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7809,7 +8838,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEDEDED"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -23685,22 +24714,28 @@
         <v>3</v>
       </c>
       <c r="G471" s="2"/>
-      <c r="H471" s="6" t="s">
+      <c r="H471" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I471" s="2" t="s">
         <v>2070</v>
       </c>
-      <c r="I471" s="2"/>
-      <c r="J471" s="2"/>
-      <c r="K471" s="2"/>
+      <c r="J471" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="K471" s="2" t="s">
+        <v>2072</v>
+      </c>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2" t="n">
         <v>471</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="D472" s="2" t="s">
         <v>13</v>
@@ -23712,22 +24747,28 @@
         <v>1</v>
       </c>
       <c r="G472" s="2"/>
-      <c r="H472" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I472" s="2"/>
-      <c r="J472" s="2"/>
-      <c r="K472" s="2"/>
+      <c r="H472" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I472" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="J472" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="K472" s="2" t="s">
+        <v>2077</v>
+      </c>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="n">
         <v>472</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>2074</v>
+        <v>2079</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>42</v>
@@ -23739,13 +24780,13 @@
         <v>1</v>
       </c>
       <c r="G473" s="2" t="s">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="H473" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I473" s="2" t="s">
-        <v>2076</v>
+        <v>2081</v>
       </c>
       <c r="J473" s="2" t="s">
         <v>47</v>
@@ -23757,7 +24798,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>2077</v>
+        <v>2082</v>
       </c>
       <c r="C474" s="2" t="s">
         <v>272</v>
@@ -23772,21 +24813,27 @@
         <v>1</v>
       </c>
       <c r="G474" s="2" t="s">
-        <v>2078</v>
-      </c>
-      <c r="H474" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I474" s="2"/>
-      <c r="J474" s="2"/>
-      <c r="K474" s="2"/>
+        <v>2083</v>
+      </c>
+      <c r="H474" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I474" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="J474" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="K474" s="2" t="s">
+        <v>2086</v>
+      </c>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="n">
         <v>474</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>2079</v>
+        <v>2087</v>
       </c>
       <c r="C475" s="2" t="s">
         <v>1264</v>
@@ -23801,22 +24848,28 @@
         <v>1</v>
       </c>
       <c r="G475" s="2"/>
-      <c r="H475" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I475" s="2"/>
-      <c r="J475" s="2"/>
-      <c r="K475" s="2"/>
+      <c r="H475" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I475" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="J475" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="K475" s="2" t="s">
+        <v>2090</v>
+      </c>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="n">
         <v>475</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>2080</v>
+        <v>2091</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>2081</v>
+        <v>2092</v>
       </c>
       <c r="D476" s="2" t="s">
         <v>61</v>
@@ -23828,24 +24881,30 @@
         <v>1</v>
       </c>
       <c r="G476" s="2" t="s">
-        <v>2082</v>
-      </c>
-      <c r="H476" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I476" s="2"/>
-      <c r="J476" s="2"/>
-      <c r="K476" s="2"/>
+        <v>2093</v>
+      </c>
+      <c r="H476" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I476" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="J476" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="K476" s="2" t="s">
+        <v>2096</v>
+      </c>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2" t="n">
         <v>476</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>2083</v>
+        <v>2097</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>2084</v>
+        <v>2098</v>
       </c>
       <c r="D477" s="2" t="s">
         <v>13</v>
@@ -23857,19 +24916,25 @@
         <v>1</v>
       </c>
       <c r="G477" s="2"/>
-      <c r="H477" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I477" s="2"/>
-      <c r="J477" s="2"/>
-      <c r="K477" s="2"/>
+      <c r="H477" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I477" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="J477" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="K477" s="2" t="s">
+        <v>2101</v>
+      </c>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2" t="n">
         <v>477</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>2085</v>
+        <v>2102</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>26</v>
@@ -23884,19 +24949,25 @@
         <v>2</v>
       </c>
       <c r="G478" s="2"/>
-      <c r="H478" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I478" s="2"/>
-      <c r="J478" s="2"/>
-      <c r="K478" s="2"/>
+      <c r="H478" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I478" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="J478" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="K478" s="2" t="s">
+        <v>2105</v>
+      </c>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="2" t="n">
         <v>478</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>2086</v>
+        <v>2106</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>1435</v>
@@ -23911,22 +24982,28 @@
         <v>2</v>
       </c>
       <c r="G479" s="2"/>
-      <c r="H479" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I479" s="2"/>
-      <c r="J479" s="2"/>
-      <c r="K479" s="2"/>
+      <c r="H479" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I479" s="2" t="s">
+        <v>2107</v>
+      </c>
+      <c r="J479" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="K479" s="2" t="s">
+        <v>2109</v>
+      </c>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="2" t="n">
         <v>479</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>2087</v>
+        <v>2110</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>2088</v>
+        <v>2111</v>
       </c>
       <c r="D480" s="2" t="s">
         <v>20</v>
@@ -23938,22 +25015,28 @@
         <v>1</v>
       </c>
       <c r="G480" s="2"/>
-      <c r="H480" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I480" s="2"/>
-      <c r="J480" s="2"/>
-      <c r="K480" s="2"/>
+      <c r="H480" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I480" s="2" t="s">
+        <v>2107</v>
+      </c>
+      <c r="J480" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="K480" s="2" t="s">
+        <v>2113</v>
+      </c>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="2" t="n">
         <v>480</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>2089</v>
+        <v>2114</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>2090</v>
+        <v>2115</v>
       </c>
       <c r="D481" s="2" t="s">
         <v>13</v>
@@ -23965,22 +25048,28 @@
         <v>1</v>
       </c>
       <c r="G481" s="2"/>
-      <c r="H481" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I481" s="2"/>
-      <c r="J481" s="2"/>
-      <c r="K481" s="2"/>
+      <c r="H481" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I481" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="J481" s="2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="K481" s="2" t="s">
+        <v>2118</v>
+      </c>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2" t="n">
         <v>481</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>2091</v>
+        <v>2119</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>2092</v>
+        <v>2120</v>
       </c>
       <c r="D482" s="2" t="s">
         <v>13</v>
@@ -23992,19 +25081,25 @@
         <v>1</v>
       </c>
       <c r="G482" s="2"/>
-      <c r="H482" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I482" s="2"/>
-      <c r="J482" s="2"/>
-      <c r="K482" s="2"/>
+      <c r="H482" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I482" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="J482" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="K482" s="2" t="s">
+        <v>2123</v>
+      </c>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2" t="n">
         <v>482</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>2093</v>
+        <v>2124</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>297</v>
@@ -24019,21 +25114,27 @@
         <v>1</v>
       </c>
       <c r="G483" s="2" t="s">
-        <v>2094</v>
-      </c>
-      <c r="H483" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I483" s="2"/>
-      <c r="J483" s="2"/>
-      <c r="K483" s="2"/>
+        <v>2125</v>
+      </c>
+      <c r="H483" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I483" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="J483" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="K483" s="2" t="s">
+        <v>2128</v>
+      </c>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2" t="n">
         <v>483</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>2095</v>
+        <v>2129</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>272</v>
@@ -24048,7 +25149,7 @@
         <v>1</v>
       </c>
       <c r="G484" s="2" t="s">
-        <v>2096</v>
+        <v>2130</v>
       </c>
       <c r="H484" s="5" t="s">
         <v>45</v>
@@ -24066,7 +25167,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>2097</v>
+        <v>2131</v>
       </c>
       <c r="C485" s="2" t="s">
         <v>1075</v>
@@ -24081,19 +25182,25 @@
         <v>1</v>
       </c>
       <c r="G485" s="2"/>
-      <c r="H485" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I485" s="2"/>
-      <c r="J485" s="2"/>
-      <c r="K485" s="2"/>
+      <c r="H485" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I485" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J485" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="K485" s="2" t="s">
+        <v>2133</v>
+      </c>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2" t="n">
         <v>485</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>2098</v>
+        <v>2134</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>1752</v>
@@ -24108,22 +25215,28 @@
         <v>1</v>
       </c>
       <c r="G486" s="2"/>
-      <c r="H486" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I486" s="2"/>
-      <c r="J486" s="2"/>
-      <c r="K486" s="2"/>
+      <c r="H486" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I486" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="J486" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="K486" s="2" t="s">
+        <v>2137</v>
+      </c>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2" t="n">
         <v>486</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>2099</v>
+        <v>2138</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>2100</v>
+        <v>2139</v>
       </c>
       <c r="D487" s="2" t="s">
         <v>20</v>
@@ -24135,22 +25248,28 @@
         <v>1</v>
       </c>
       <c r="G487" s="2"/>
-      <c r="H487" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I487" s="2"/>
-      <c r="J487" s="2"/>
-      <c r="K487" s="2"/>
+      <c r="H487" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I487" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="J487" s="2" t="s">
+        <v>2141</v>
+      </c>
+      <c r="K487" s="2" t="s">
+        <v>2142</v>
+      </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="2" t="n">
         <v>487</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>2101</v>
+        <v>2143</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>2102</v>
+        <v>2144</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>13</v>
@@ -24162,11 +25281,15 @@
         <v>1</v>
       </c>
       <c r="G488" s="2"/>
-      <c r="H488" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I488" s="2"/>
-      <c r="J488" s="2"/>
+      <c r="H488" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I488" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J488" s="2" t="s">
+        <v>2145</v>
+      </c>
       <c r="K488" s="2"/>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24174,10 +25297,10 @@
         <v>488</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>2103</v>
+        <v>2146</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>2104</v>
+        <v>2147</v>
       </c>
       <c r="D489" s="2" t="s">
         <v>42</v>
@@ -24189,24 +25312,30 @@
         <v>1</v>
       </c>
       <c r="G489" s="2" t="s">
-        <v>2105</v>
-      </c>
-      <c r="H489" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I489" s="2"/>
-      <c r="J489" s="2"/>
-      <c r="K489" s="2"/>
+        <v>2148</v>
+      </c>
+      <c r="H489" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I489" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="J489" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="K489" s="2" t="s">
+        <v>2151</v>
+      </c>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="2" t="n">
         <v>489</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>2106</v>
+        <v>2152</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>2107</v>
+        <v>2153</v>
       </c>
       <c r="D490" s="2" t="s">
         <v>98</v>
@@ -24218,22 +25347,28 @@
         <v>2</v>
       </c>
       <c r="G490" s="2"/>
-      <c r="H490" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I490" s="2"/>
-      <c r="J490" s="2"/>
-      <c r="K490" s="2"/>
+      <c r="H490" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I490" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="J490" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="K490" s="2" t="s">
+        <v>2156</v>
+      </c>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="2" t="n">
         <v>490</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>2108</v>
+        <v>2157</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>2109</v>
+        <v>2158</v>
       </c>
       <c r="D491" s="2" t="s">
         <v>13</v>
@@ -24245,11 +25380,13 @@
         <v>2</v>
       </c>
       <c r="G491" s="2"/>
-      <c r="H491" s="6" t="s">
-        <v>2070</v>
+      <c r="H491" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="I491" s="2"/>
-      <c r="J491" s="2"/>
+      <c r="J491" s="2" t="s">
+        <v>2159</v>
+      </c>
       <c r="K491" s="2"/>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24257,7 +25394,7 @@
         <v>491</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>2110</v>
+        <v>2160</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>627</v>
@@ -24279,10 +25416,10 @@
         <v>176</v>
       </c>
       <c r="J492" s="2" t="s">
-        <v>2111</v>
+        <v>2161</v>
       </c>
       <c r="K492" s="2" t="s">
-        <v>2112</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24290,7 +25427,7 @@
         <v>492</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>2113</v>
+        <v>2163</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>515</v>
@@ -24309,13 +25446,13 @@
         <v>45</v>
       </c>
       <c r="I493" s="2" t="s">
-        <v>2114</v>
+        <v>2164</v>
       </c>
       <c r="J493" s="2" t="s">
-        <v>2115</v>
+        <v>2165</v>
       </c>
       <c r="K493" s="2" t="s">
-        <v>2116</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24323,7 +25460,7 @@
         <v>493</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>2117</v>
+        <v>2167</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>1101</v>
@@ -24338,7 +25475,7 @@
         <v>1</v>
       </c>
       <c r="G494" s="2" t="s">
-        <v>2118</v>
+        <v>2168</v>
       </c>
       <c r="H494" s="3" t="s">
         <v>15</v>
@@ -24347,7 +25484,7 @@
         <v>16</v>
       </c>
       <c r="J494" s="2" t="s">
-        <v>2119</v>
+        <v>2169</v>
       </c>
       <c r="K494" s="2"/>
     </row>
@@ -24356,7 +25493,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>2120</v>
+        <v>2170</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>229</v>
@@ -24378,10 +25515,10 @@
         <v>710</v>
       </c>
       <c r="J495" s="2" t="s">
-        <v>2121</v>
+        <v>2171</v>
       </c>
       <c r="K495" s="2" t="s">
-        <v>2122</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24392,7 +25529,7 @@
         <v>1089</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>2123</v>
+        <v>2173</v>
       </c>
       <c r="D496" s="2" t="s">
         <v>13</v>
@@ -24408,13 +25545,13 @@
         <v>21</v>
       </c>
       <c r="I496" s="2" t="s">
-        <v>2124</v>
+        <v>2174</v>
       </c>
       <c r="J496" s="2" t="s">
-        <v>2125</v>
+        <v>2175</v>
       </c>
       <c r="K496" s="2" t="s">
-        <v>2126</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24422,10 +25559,10 @@
         <v>496</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>2127</v>
+        <v>2177</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>2128</v>
+        <v>2178</v>
       </c>
       <c r="D497" s="2" t="s">
         <v>20</v>
@@ -24441,13 +25578,13 @@
         <v>45</v>
       </c>
       <c r="I497" s="2" t="s">
-        <v>2129</v>
+        <v>2179</v>
       </c>
       <c r="J497" s="2" t="s">
-        <v>2130</v>
+        <v>2180</v>
       </c>
       <c r="K497" s="2" t="s">
-        <v>2131</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24455,10 +25592,10 @@
         <v>497</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>2132</v>
+        <v>2182</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="D498" s="2" t="s">
         <v>314</v>
@@ -24470,7 +25607,7 @@
         <v>2</v>
       </c>
       <c r="G498" s="2" t="s">
-        <v>2133</v>
+        <v>2183</v>
       </c>
       <c r="H498" s="4" t="s">
         <v>21</v>
@@ -24479,10 +25616,10 @@
         <v>927</v>
       </c>
       <c r="J498" s="2" t="s">
-        <v>2134</v>
+        <v>2184</v>
       </c>
       <c r="K498" s="2" t="s">
-        <v>2135</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24490,10 +25627,10 @@
         <v>498</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>2136</v>
+        <v>2186</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>2137</v>
+        <v>2187</v>
       </c>
       <c r="D499" s="2" t="s">
         <v>20</v>
@@ -24509,13 +25646,13 @@
         <v>21</v>
       </c>
       <c r="I499" s="2" t="s">
-        <v>2138</v>
+        <v>2188</v>
       </c>
       <c r="J499" s="2" t="s">
-        <v>2139</v>
+        <v>2189</v>
       </c>
       <c r="K499" s="2" t="s">
-        <v>2140</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24523,7 +25660,7 @@
         <v>499</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>2141</v>
+        <v>2191</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>1263</v>
@@ -24542,13 +25679,13 @@
         <v>21</v>
       </c>
       <c r="I500" s="2" t="s">
-        <v>2142</v>
+        <v>2192</v>
       </c>
       <c r="J500" s="2" t="s">
-        <v>2143</v>
+        <v>2193</v>
       </c>
       <c r="K500" s="2" t="s">
-        <v>2144</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24556,10 +25693,10 @@
         <v>500</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>2145</v>
+        <v>2195</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>2146</v>
+        <v>2196</v>
       </c>
       <c r="D501" s="2" t="s">
         <v>42</v>
@@ -24571,21 +25708,27 @@
         <v>1</v>
       </c>
       <c r="G501" s="2" t="s">
-        <v>2147</v>
-      </c>
-      <c r="H501" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I501" s="2"/>
-      <c r="J501" s="2"/>
-      <c r="K501" s="2"/>
+        <v>2197</v>
+      </c>
+      <c r="H501" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I501" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="J501" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="K501" s="2" t="s">
+        <v>2200</v>
+      </c>
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2" t="n">
         <v>501</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>2148</v>
+        <v>2201</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>1513</v>
@@ -24600,11 +25743,13 @@
         <v>1</v>
       </c>
       <c r="G502" s="2"/>
-      <c r="H502" s="6" t="s">
-        <v>2070</v>
+      <c r="H502" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="I502" s="2"/>
-      <c r="J502" s="2"/>
+      <c r="J502" s="2" t="s">
+        <v>2202</v>
+      </c>
       <c r="K502" s="2"/>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24612,10 +25757,10 @@
         <v>502</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>2148</v>
+        <v>2201</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>2149</v>
+        <v>2203</v>
       </c>
       <c r="D503" s="2" t="s">
         <v>13</v>
@@ -24634,10 +25779,10 @@
         <v>710</v>
       </c>
       <c r="J503" s="2" t="s">
-        <v>2150</v>
+        <v>2204</v>
       </c>
       <c r="K503" s="2" t="s">
-        <v>2151</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24645,7 +25790,7 @@
         <v>503</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>2152</v>
+        <v>2206</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>1674</v>
@@ -24660,13 +25805,13 @@
         <v>1</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>2153</v>
+        <v>2207</v>
       </c>
       <c r="H504" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I504" s="2" t="s">
-        <v>2154</v>
+        <v>2208</v>
       </c>
       <c r="J504" s="2" t="s">
         <v>47</v>
@@ -24678,10 +25823,10 @@
         <v>504</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>2155</v>
+        <v>2209</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>2156</v>
+        <v>2210</v>
       </c>
       <c r="D505" s="2" t="s">
         <v>98</v>
@@ -24693,22 +25838,28 @@
         <v>2</v>
       </c>
       <c r="G505" s="2"/>
-      <c r="H505" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I505" s="2"/>
-      <c r="J505" s="2"/>
-      <c r="K505" s="2"/>
+      <c r="H505" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I505" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="J505" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="K505" s="2" t="s">
+        <v>2213</v>
+      </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2" t="n">
         <v>505</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>2157</v>
+        <v>2214</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>2158</v>
+        <v>2215</v>
       </c>
       <c r="D506" s="2" t="s">
         <v>258</v>
@@ -24720,24 +25871,30 @@
         <v>3</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>2159</v>
-      </c>
-      <c r="H506" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I506" s="2"/>
-      <c r="J506" s="2"/>
-      <c r="K506" s="2"/>
+        <v>2216</v>
+      </c>
+      <c r="H506" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I506" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J506" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="K506" s="2" t="s">
+        <v>2218</v>
+      </c>
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2" t="n">
         <v>506</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>2157</v>
+        <v>2214</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>2160</v>
+        <v>2219</v>
       </c>
       <c r="D507" s="2" t="s">
         <v>61</v>
@@ -24749,24 +25906,30 @@
         <v>2</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>2161</v>
-      </c>
-      <c r="H507" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I507" s="2"/>
-      <c r="J507" s="2"/>
-      <c r="K507" s="2"/>
+        <v>2220</v>
+      </c>
+      <c r="H507" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I507" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="J507" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="K507" s="2" t="s">
+        <v>2222</v>
+      </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2" t="n">
         <v>507</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>2162</v>
+        <v>2223</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>2163</v>
+        <v>2224</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>13</v>
@@ -24778,19 +25941,25 @@
         <v>1</v>
       </c>
       <c r="G508" s="2"/>
-      <c r="H508" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I508" s="2"/>
-      <c r="J508" s="2"/>
-      <c r="K508" s="2"/>
+      <c r="H508" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I508" s="2" t="s">
+        <v>2225</v>
+      </c>
+      <c r="J508" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="K508" s="2" t="s">
+        <v>2227</v>
+      </c>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2" t="n">
         <v>508</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>2162</v>
+        <v>2223</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>383</v>
@@ -24805,19 +25974,25 @@
         <v>1</v>
       </c>
       <c r="G509" s="2"/>
-      <c r="H509" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I509" s="2"/>
-      <c r="J509" s="2"/>
-      <c r="K509" s="2"/>
+      <c r="H509" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I509" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="J509" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="K509" s="2" t="s">
+        <v>2230</v>
+      </c>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2" t="n">
         <v>509</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>2164</v>
+        <v>2231</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>201</v>
@@ -24832,24 +26007,30 @@
         <v>1</v>
       </c>
       <c r="G510" s="2" t="s">
-        <v>2165</v>
-      </c>
-      <c r="H510" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I510" s="2"/>
-      <c r="J510" s="2"/>
-      <c r="K510" s="2"/>
+        <v>2232</v>
+      </c>
+      <c r="H510" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I510" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="J510" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="K510" s="2" t="s">
+        <v>2234</v>
+      </c>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="2" t="n">
         <v>510</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>2166</v>
+        <v>2235</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>2167</v>
+        <v>2236</v>
       </c>
       <c r="D511" s="2" t="s">
         <v>13</v>
@@ -24861,22 +26042,28 @@
         <v>1</v>
       </c>
       <c r="G511" s="2"/>
-      <c r="H511" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I511" s="2"/>
-      <c r="J511" s="2"/>
-      <c r="K511" s="2"/>
+      <c r="H511" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I511" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J511" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="K511" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2" t="n">
         <v>511</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>2168</v>
+        <v>2238</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>2169</v>
+        <v>2239</v>
       </c>
       <c r="D512" s="2" t="s">
         <v>13</v>
@@ -24888,22 +26075,28 @@
         <v>2</v>
       </c>
       <c r="G512" s="2"/>
-      <c r="H512" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I512" s="2"/>
-      <c r="J512" s="2"/>
-      <c r="K512" s="2"/>
+      <c r="H512" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I512" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J512" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="K512" s="2" t="s">
+        <v>2241</v>
+      </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2" t="n">
         <v>512</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>2170</v>
+        <v>2242</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>2171</v>
+        <v>2243</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>13</v>
@@ -24915,22 +26108,28 @@
         <v>2</v>
       </c>
       <c r="G513" s="2"/>
-      <c r="H513" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I513" s="2"/>
-      <c r="J513" s="2"/>
-      <c r="K513" s="2"/>
+      <c r="H513" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I513" s="2" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J513" s="2" t="s">
+        <v>2245</v>
+      </c>
+      <c r="K513" s="2" t="s">
+        <v>2246</v>
+      </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2" t="n">
         <v>513</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>2172</v>
+        <v>2247</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>2173</v>
+        <v>2248</v>
       </c>
       <c r="D514" s="2" t="s">
         <v>20</v>
@@ -24942,11 +26141,13 @@
         <v>1</v>
       </c>
       <c r="G514" s="2"/>
-      <c r="H514" s="6" t="s">
-        <v>2070</v>
+      <c r="H514" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="I514" s="2"/>
-      <c r="J514" s="2"/>
+      <c r="J514" s="2" t="s">
+        <v>2249</v>
+      </c>
       <c r="K514" s="2"/>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24954,10 +26155,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>2174</v>
+        <v>2250</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>2175</v>
+        <v>2251</v>
       </c>
       <c r="D515" s="2" t="s">
         <v>20</v>
@@ -24969,22 +26170,28 @@
         <v>1</v>
       </c>
       <c r="G515" s="2"/>
-      <c r="H515" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I515" s="2"/>
-      <c r="J515" s="2"/>
-      <c r="K515" s="2"/>
+      <c r="H515" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I515" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J515" s="2" t="s">
+        <v>2252</v>
+      </c>
+      <c r="K515" s="2" t="s">
+        <v>2253</v>
+      </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="n">
         <v>515</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>2176</v>
+        <v>2254</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>2177</v>
+        <v>2255</v>
       </c>
       <c r="D516" s="2" t="s">
         <v>13</v>
@@ -24996,19 +26203,25 @@
         <v>2</v>
       </c>
       <c r="G516" s="2"/>
-      <c r="H516" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I516" s="2"/>
-      <c r="J516" s="2"/>
-      <c r="K516" s="2"/>
+      <c r="H516" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I516" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="J516" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="K516" s="2" t="s">
+        <v>2257</v>
+      </c>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="n">
         <v>516</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>2176</v>
+        <v>2254</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>175</v>
@@ -25023,22 +26236,28 @@
         <v>1</v>
       </c>
       <c r="G517" s="2"/>
-      <c r="H517" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I517" s="2"/>
-      <c r="J517" s="2"/>
-      <c r="K517" s="2"/>
+      <c r="H517" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I517" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="J517" s="2" t="s">
+        <v>2259</v>
+      </c>
+      <c r="K517" s="2" t="s">
+        <v>2260</v>
+      </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="2" t="n">
         <v>517</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>2178</v>
+        <v>2261</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>2179</v>
+        <v>2262</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>258</v>
@@ -25050,24 +26269,30 @@
         <v>4</v>
       </c>
       <c r="G518" s="2" t="s">
-        <v>2180</v>
-      </c>
-      <c r="H518" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I518" s="2"/>
-      <c r="J518" s="2"/>
-      <c r="K518" s="2"/>
+        <v>2263</v>
+      </c>
+      <c r="H518" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I518" s="2" t="s">
+        <v>2264</v>
+      </c>
+      <c r="J518" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="K518" s="2" t="s">
+        <v>2266</v>
+      </c>
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="2" t="n">
         <v>518</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>2181</v>
+        <v>2267</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>2182</v>
+        <v>2268</v>
       </c>
       <c r="D519" s="2" t="s">
         <v>61</v>
@@ -25079,24 +26304,30 @@
         <v>1</v>
       </c>
       <c r="G519" s="2" t="s">
-        <v>2183</v>
-      </c>
-      <c r="H519" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I519" s="2"/>
-      <c r="J519" s="2"/>
-      <c r="K519" s="2"/>
+        <v>2269</v>
+      </c>
+      <c r="H519" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I519" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J519" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="K519" s="2" t="s">
+        <v>2271</v>
+      </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="2" t="n">
         <v>519</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>2184</v>
+        <v>2272</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>2185</v>
+        <v>2273</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>20</v>
@@ -25108,11 +26339,15 @@
         <v>3</v>
       </c>
       <c r="G520" s="2"/>
-      <c r="H520" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I520" s="2"/>
-      <c r="J520" s="2"/>
+      <c r="H520" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I520" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J520" s="2" t="s">
+        <v>2274</v>
+      </c>
       <c r="K520" s="2"/>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25120,7 +26355,7 @@
         <v>520</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>2184</v>
+        <v>2272</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>591</v>
@@ -25135,19 +26370,25 @@
         <v>1</v>
       </c>
       <c r="G521" s="2"/>
-      <c r="H521" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I521" s="2"/>
-      <c r="J521" s="2"/>
-      <c r="K521" s="2"/>
+      <c r="H521" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I521" s="2" t="s">
+        <v>2275</v>
+      </c>
+      <c r="J521" s="2" t="s">
+        <v>2276</v>
+      </c>
+      <c r="K521" s="2" t="s">
+        <v>2277</v>
+      </c>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2" t="n">
         <v>521</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>2186</v>
+        <v>2278</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>157</v>
@@ -25162,22 +26403,28 @@
         <v>1</v>
       </c>
       <c r="G522" s="2"/>
-      <c r="H522" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I522" s="2"/>
-      <c r="J522" s="2"/>
-      <c r="K522" s="2"/>
+      <c r="H522" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I522" s="2" t="s">
+        <v>2279</v>
+      </c>
+      <c r="J522" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="K522" s="2" t="s">
+        <v>2281</v>
+      </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2" t="n">
         <v>522</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>2187</v>
+        <v>2282</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>2188</v>
+        <v>2283</v>
       </c>
       <c r="D523" s="2" t="s">
         <v>42</v>
@@ -25189,13 +26436,13 @@
         <v>1</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>2189</v>
+        <v>2284</v>
       </c>
       <c r="H523" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>2190</v>
+        <v>2285</v>
       </c>
       <c r="J523" s="2" t="s">
         <v>47</v>
@@ -25207,7 +26454,7 @@
         <v>523</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>2191</v>
+        <v>2286</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>201</v>
@@ -25222,19 +26469,25 @@
         <v>1</v>
       </c>
       <c r="G524" s="2"/>
-      <c r="H524" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I524" s="2"/>
-      <c r="J524" s="2"/>
-      <c r="K524" s="2"/>
+      <c r="H524" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I524" s="2" t="s">
+        <v>2287</v>
+      </c>
+      <c r="J524" s="2" t="s">
+        <v>2288</v>
+      </c>
+      <c r="K524" s="2" t="s">
+        <v>2289</v>
+      </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2" t="n">
         <v>524</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>2192</v>
+        <v>2290</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>957</v>
@@ -25249,21 +26502,27 @@
         <v>2</v>
       </c>
       <c r="G525" s="2" t="s">
-        <v>2193</v>
-      </c>
-      <c r="H525" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I525" s="2"/>
-      <c r="J525" s="2"/>
-      <c r="K525" s="2"/>
+        <v>2291</v>
+      </c>
+      <c r="H525" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I525" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J525" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="K525" s="2" t="s">
+        <v>2293</v>
+      </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2" t="n">
         <v>525</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>2194</v>
+        <v>2294</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>1650</v>
@@ -25278,21 +26537,27 @@
         <v>1</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>2195</v>
-      </c>
-      <c r="H526" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I526" s="2"/>
-      <c r="J526" s="2"/>
-      <c r="K526" s="2"/>
+        <v>2295</v>
+      </c>
+      <c r="H526" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I526" s="2" t="s">
+        <v>2296</v>
+      </c>
+      <c r="J526" s="2" t="s">
+        <v>2297</v>
+      </c>
+      <c r="K526" s="2" t="s">
+        <v>2298</v>
+      </c>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2" t="n">
         <v>526</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>2196</v>
+        <v>2299</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>1727</v>
@@ -25307,19 +26572,25 @@
         <v>1</v>
       </c>
       <c r="G527" s="2"/>
-      <c r="H527" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I527" s="2"/>
-      <c r="J527" s="2"/>
-      <c r="K527" s="2"/>
+      <c r="H527" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I527" s="2" t="s">
+        <v>2300</v>
+      </c>
+      <c r="J527" s="2" t="s">
+        <v>2301</v>
+      </c>
+      <c r="K527" s="2" t="s">
+        <v>2302</v>
+      </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="2" t="n">
         <v>527</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>2197</v>
+        <v>2303</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>627</v>
@@ -25334,22 +26605,28 @@
         <v>2</v>
       </c>
       <c r="G528" s="2"/>
-      <c r="H528" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I528" s="2"/>
-      <c r="J528" s="2"/>
-      <c r="K528" s="2"/>
+      <c r="H528" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I528" s="2" t="s">
+        <v>2304</v>
+      </c>
+      <c r="J528" s="2" t="s">
+        <v>2305</v>
+      </c>
+      <c r="K528" s="2" t="s">
+        <v>2306</v>
+      </c>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="2" t="n">
         <v>528</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>2197</v>
+        <v>2303</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>2198</v>
+        <v>2307</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>13</v>
@@ -25361,11 +26638,15 @@
         <v>1</v>
       </c>
       <c r="G529" s="2"/>
-      <c r="H529" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I529" s="2"/>
-      <c r="J529" s="2"/>
+      <c r="H529" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I529" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J529" s="2" t="s">
+        <v>2308</v>
+      </c>
       <c r="K529" s="2"/>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25373,7 +26654,7 @@
         <v>529</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>2197</v>
+        <v>2303</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>1089</v>
@@ -25388,22 +26669,28 @@
         <v>2</v>
       </c>
       <c r="G530" s="2"/>
-      <c r="H530" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I530" s="2"/>
-      <c r="J530" s="2"/>
-      <c r="K530" s="2"/>
+      <c r="H530" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I530" s="2" t="s">
+        <v>2309</v>
+      </c>
+      <c r="J530" s="2" t="s">
+        <v>2310</v>
+      </c>
+      <c r="K530" s="2" t="s">
+        <v>2311</v>
+      </c>
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="2" t="n">
         <v>530</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>2199</v>
+        <v>2312</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>2185</v>
+        <v>2273</v>
       </c>
       <c r="D531" s="2" t="s">
         <v>42</v>
@@ -25415,21 +26702,27 @@
         <v>1</v>
       </c>
       <c r="G531" s="2" t="s">
-        <v>2200</v>
-      </c>
-      <c r="H531" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I531" s="2"/>
-      <c r="J531" s="2"/>
-      <c r="K531" s="2"/>
+        <v>2313</v>
+      </c>
+      <c r="H531" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I531" s="2" t="s">
+        <v>2314</v>
+      </c>
+      <c r="J531" s="2" t="s">
+        <v>2315</v>
+      </c>
+      <c r="K531" s="2" t="s">
+        <v>2316</v>
+      </c>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2" t="n">
         <v>531</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>2201</v>
+        <v>2317</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>297</v>
@@ -25444,24 +26737,30 @@
         <v>2</v>
       </c>
       <c r="G532" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="H532" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I532" s="2"/>
-      <c r="J532" s="2"/>
-      <c r="K532" s="2"/>
+        <v>2318</v>
+      </c>
+      <c r="H532" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I532" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="J532" s="2" t="s">
+        <v>2319</v>
+      </c>
+      <c r="K532" s="2" t="s">
+        <v>2320</v>
+      </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="n">
         <v>532</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>2203</v>
+        <v>2321</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>2204</v>
+        <v>2322</v>
       </c>
       <c r="D533" s="2" t="s">
         <v>13</v>
@@ -25473,11 +26772,15 @@
         <v>1</v>
       </c>
       <c r="G533" s="2"/>
-      <c r="H533" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I533" s="2"/>
-      <c r="J533" s="2"/>
+      <c r="H533" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I533" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J533" s="2" t="s">
+        <v>2323</v>
+      </c>
       <c r="K533" s="2"/>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25488,7 +26791,7 @@
         <v>1124</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>2205</v>
+        <v>2324</v>
       </c>
       <c r="D534" s="2" t="s">
         <v>42</v>
@@ -25500,7 +26803,7 @@
         <v>1</v>
       </c>
       <c r="G534" s="2" t="s">
-        <v>2206</v>
+        <v>2325</v>
       </c>
       <c r="H534" s="5" t="s">
         <v>45</v>
@@ -25518,10 +26821,10 @@
         <v>534</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>2207</v>
+        <v>2326</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>2208</v>
+        <v>2327</v>
       </c>
       <c r="D535" s="2" t="s">
         <v>13</v>
@@ -25533,22 +26836,28 @@
         <v>3</v>
       </c>
       <c r="G535" s="2"/>
-      <c r="H535" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I535" s="2"/>
-      <c r="J535" s="2"/>
-      <c r="K535" s="2"/>
+      <c r="H535" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I535" s="2" t="s">
+        <v>2328</v>
+      </c>
+      <c r="J535" s="2" t="s">
+        <v>2329</v>
+      </c>
+      <c r="K535" s="2" t="s">
+        <v>2330</v>
+      </c>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2" t="n">
         <v>535</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>2209</v>
+        <v>2331</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>2210</v>
+        <v>2332</v>
       </c>
       <c r="D536" s="2" t="s">
         <v>13</v>
@@ -25560,22 +26869,28 @@
         <v>1</v>
       </c>
       <c r="G536" s="2"/>
-      <c r="H536" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I536" s="2"/>
-      <c r="J536" s="2"/>
-      <c r="K536" s="2"/>
+      <c r="H536" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I536" s="2" t="s">
+        <v>2333</v>
+      </c>
+      <c r="J536" s="2" t="s">
+        <v>2334</v>
+      </c>
+      <c r="K536" s="2" t="s">
+        <v>2335</v>
+      </c>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2" t="n">
         <v>536</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>2211</v>
+        <v>2336</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>2212</v>
+        <v>2337</v>
       </c>
       <c r="D537" s="2" t="s">
         <v>13</v>
@@ -25587,19 +26902,25 @@
         <v>1</v>
       </c>
       <c r="G537" s="2"/>
-      <c r="H537" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I537" s="2"/>
-      <c r="J537" s="2"/>
-      <c r="K537" s="2"/>
+      <c r="H537" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I537" s="2" t="s">
+        <v>2338</v>
+      </c>
+      <c r="J537" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="K537" s="2" t="s">
+        <v>2340</v>
+      </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="2" t="n">
         <v>537</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>2213</v>
+        <v>2341</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>1280</v>
@@ -25614,19 +26935,25 @@
         <v>2</v>
       </c>
       <c r="G538" s="2"/>
-      <c r="H538" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I538" s="2"/>
-      <c r="J538" s="2"/>
-      <c r="K538" s="2"/>
+      <c r="H538" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I538" s="2" t="s">
+        <v>2342</v>
+      </c>
+      <c r="J538" s="2" t="s">
+        <v>2343</v>
+      </c>
+      <c r="K538" s="2" t="s">
+        <v>2344</v>
+      </c>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="2" t="n">
         <v>538</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>2214</v>
+        <v>2345</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>689</v>
@@ -25641,22 +26968,28 @@
         <v>1</v>
       </c>
       <c r="G539" s="2"/>
-      <c r="H539" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I539" s="2"/>
-      <c r="J539" s="2"/>
-      <c r="K539" s="2"/>
+      <c r="H539" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I539" s="2" t="s">
+        <v>2346</v>
+      </c>
+      <c r="J539" s="2" t="s">
+        <v>2347</v>
+      </c>
+      <c r="K539" s="2" t="s">
+        <v>2348</v>
+      </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="2" t="n">
         <v>539</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>2215</v>
+        <v>2349</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>2216</v>
+        <v>2350</v>
       </c>
       <c r="D540" s="2" t="s">
         <v>13</v>
@@ -25668,22 +27001,28 @@
         <v>1</v>
       </c>
       <c r="G540" s="2"/>
-      <c r="H540" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I540" s="2"/>
-      <c r="J540" s="2"/>
-      <c r="K540" s="2"/>
+      <c r="H540" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I540" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J540" s="2" t="s">
+        <v>2351</v>
+      </c>
+      <c r="K540" s="2" t="s">
+        <v>2352</v>
+      </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="2" t="n">
         <v>540</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>2215</v>
+        <v>2349</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>2217</v>
+        <v>2353</v>
       </c>
       <c r="D541" s="2" t="s">
         <v>61</v>
@@ -25695,24 +27034,30 @@
         <v>2</v>
       </c>
       <c r="G541" s="2" t="s">
-        <v>2218</v>
-      </c>
-      <c r="H541" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I541" s="2"/>
-      <c r="J541" s="2"/>
-      <c r="K541" s="2"/>
+        <v>2354</v>
+      </c>
+      <c r="H541" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I541" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J541" s="2" t="s">
+        <v>2355</v>
+      </c>
+      <c r="K541" s="2" t="s">
+        <v>2356</v>
+      </c>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="2" t="n">
         <v>541</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>2219</v>
+        <v>2357</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>2220</v>
+        <v>2358</v>
       </c>
       <c r="D542" s="2" t="s">
         <v>42</v>
@@ -25724,24 +27069,30 @@
         <v>1</v>
       </c>
       <c r="G542" s="2" t="s">
-        <v>2221</v>
-      </c>
-      <c r="H542" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I542" s="2"/>
-      <c r="J542" s="2"/>
-      <c r="K542" s="2"/>
+        <v>2359</v>
+      </c>
+      <c r="H542" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I542" s="2" t="s">
+        <v>2360</v>
+      </c>
+      <c r="J542" s="2" t="s">
+        <v>2361</v>
+      </c>
+      <c r="K542" s="2" t="s">
+        <v>2362</v>
+      </c>
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="2" t="n">
         <v>542</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>2222</v>
+        <v>2363</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>2223</v>
+        <v>2364</v>
       </c>
       <c r="D543" s="2" t="s">
         <v>13</v>
@@ -25753,11 +27104,15 @@
         <v>1</v>
       </c>
       <c r="G543" s="2"/>
-      <c r="H543" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I543" s="2"/>
-      <c r="J543" s="2"/>
+      <c r="H543" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I543" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J543" s="2" t="s">
+        <v>2365</v>
+      </c>
       <c r="K543" s="2"/>
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25765,10 +27120,10 @@
         <v>543</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>2224</v>
+        <v>2366</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>2225</v>
+        <v>2367</v>
       </c>
       <c r="D544" s="2" t="s">
         <v>13</v>
@@ -25780,22 +27135,28 @@
         <v>2</v>
       </c>
       <c r="G544" s="2"/>
-      <c r="H544" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I544" s="2"/>
-      <c r="J544" s="2"/>
-      <c r="K544" s="2"/>
+      <c r="H544" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I544" s="2" t="s">
+        <v>2368</v>
+      </c>
+      <c r="J544" s="2" t="s">
+        <v>2369</v>
+      </c>
+      <c r="K544" s="2" t="s">
+        <v>2370</v>
+      </c>
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="2" t="n">
         <v>544</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>2226</v>
+        <v>2371</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>2227</v>
+        <v>2372</v>
       </c>
       <c r="D545" s="2" t="s">
         <v>20</v>
@@ -25807,19 +27168,25 @@
         <v>1</v>
       </c>
       <c r="G545" s="2"/>
-      <c r="H545" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I545" s="2"/>
-      <c r="J545" s="2"/>
-      <c r="K545" s="2"/>
+      <c r="H545" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I545" s="2" t="s">
+        <v>2373</v>
+      </c>
+      <c r="J545" s="2" t="s">
+        <v>2374</v>
+      </c>
+      <c r="K545" s="2" t="s">
+        <v>2375</v>
+      </c>
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2" t="n">
         <v>545</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>2228</v>
+        <v>2376</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>627</v>
@@ -25834,22 +27201,28 @@
         <v>1</v>
       </c>
       <c r="G546" s="2"/>
-      <c r="H546" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I546" s="2"/>
-      <c r="J546" s="2"/>
-      <c r="K546" s="2"/>
+      <c r="H546" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I546" s="2" t="s">
+        <v>2377</v>
+      </c>
+      <c r="J546" s="2" t="s">
+        <v>2378</v>
+      </c>
+      <c r="K546" s="2" t="s">
+        <v>2379</v>
+      </c>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2" t="n">
         <v>546</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>2229</v>
+        <v>2380</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>2230</v>
+        <v>2381</v>
       </c>
       <c r="D547" s="2" t="s">
         <v>20</v>
@@ -25865,13 +27238,13 @@
         <v>21</v>
       </c>
       <c r="I547" s="2" t="s">
-        <v>2231</v>
+        <v>2382</v>
       </c>
       <c r="J547" s="2" t="s">
-        <v>2232</v>
+        <v>2383</v>
       </c>
       <c r="K547" s="2" t="s">
-        <v>2233</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25879,10 +27252,10 @@
         <v>547</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>2234</v>
+        <v>2385</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>2235</v>
+        <v>2386</v>
       </c>
       <c r="D548" s="2" t="s">
         <v>20</v>
@@ -25898,13 +27271,13 @@
         <v>45</v>
       </c>
       <c r="I548" s="2" t="s">
-        <v>2236</v>
+        <v>2387</v>
       </c>
       <c r="J548" s="2" t="s">
-        <v>2237</v>
+        <v>2388</v>
       </c>
       <c r="K548" s="2" t="s">
-        <v>2238</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25912,10 +27285,10 @@
         <v>548</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>2239</v>
+        <v>2390</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>2240</v>
+        <v>2391</v>
       </c>
       <c r="D549" s="2" t="s">
         <v>98</v>
@@ -25931,13 +27304,13 @@
         <v>21</v>
       </c>
       <c r="I549" s="2" t="s">
-        <v>2241</v>
+        <v>2392</v>
       </c>
       <c r="J549" s="2" t="s">
-        <v>2242</v>
+        <v>2393</v>
       </c>
       <c r="K549" s="2" t="s">
-        <v>2243</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25945,10 +27318,10 @@
         <v>549</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>2239</v>
+        <v>2390</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>2244</v>
+        <v>2395</v>
       </c>
       <c r="D550" s="2" t="s">
         <v>98</v>
@@ -25967,10 +27340,10 @@
         <v>1036</v>
       </c>
       <c r="J550" s="2" t="s">
-        <v>2245</v>
+        <v>2396</v>
       </c>
       <c r="K550" s="2" t="s">
-        <v>2246</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25978,10 +27351,10 @@
         <v>550</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>2239</v>
+        <v>2390</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>2247</v>
+        <v>2398</v>
       </c>
       <c r="D551" s="2" t="s">
         <v>61</v>
@@ -25993,19 +27366,19 @@
         <v>1</v>
       </c>
       <c r="G551" s="2" t="s">
-        <v>2248</v>
+        <v>2399</v>
       </c>
       <c r="H551" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I551" s="2" t="s">
-        <v>2249</v>
+        <v>2400</v>
       </c>
       <c r="J551" s="2" t="s">
-        <v>2250</v>
+        <v>2401</v>
       </c>
       <c r="K551" s="2" t="s">
-        <v>2251</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26013,10 +27386,10 @@
         <v>551</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>2239</v>
+        <v>2390</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>2252</v>
+        <v>2403</v>
       </c>
       <c r="D552" s="2" t="s">
         <v>61</v>
@@ -26028,7 +27401,7 @@
         <v>1</v>
       </c>
       <c r="G552" s="2" t="s">
-        <v>2253</v>
+        <v>2404</v>
       </c>
       <c r="H552" s="4" t="s">
         <v>21</v>
@@ -26037,10 +27410,10 @@
         <v>576</v>
       </c>
       <c r="J552" s="2" t="s">
-        <v>2254</v>
+        <v>2405</v>
       </c>
       <c r="K552" s="2" t="s">
-        <v>2255</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26048,10 +27421,10 @@
         <v>552</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>2256</v>
+        <v>2407</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>2257</v>
+        <v>2408</v>
       </c>
       <c r="D553" s="2" t="s">
         <v>20</v>
@@ -26070,7 +27443,7 @@
         <v>16</v>
       </c>
       <c r="J553" s="2" t="s">
-        <v>2258</v>
+        <v>2409</v>
       </c>
       <c r="K553" s="2"/>
     </row>
@@ -26079,10 +27452,10 @@
         <v>553</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>2259</v>
+        <v>2410</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>2260</v>
+        <v>2411</v>
       </c>
       <c r="D554" s="2" t="s">
         <v>20</v>
@@ -26098,13 +27471,13 @@
         <v>45</v>
       </c>
       <c r="I554" s="2" t="s">
-        <v>2261</v>
+        <v>2412</v>
       </c>
       <c r="J554" s="2" t="s">
-        <v>2262</v>
+        <v>2413</v>
       </c>
       <c r="K554" s="2" t="s">
-        <v>2263</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26112,10 +27485,10 @@
         <v>554</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>2264</v>
+        <v>2415</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>2156</v>
+        <v>2210</v>
       </c>
       <c r="D555" s="2" t="s">
         <v>13</v>
@@ -26127,22 +27500,28 @@
         <v>2</v>
       </c>
       <c r="G555" s="2"/>
-      <c r="H555" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I555" s="2"/>
-      <c r="J555" s="2"/>
-      <c r="K555" s="2"/>
+      <c r="H555" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I555" s="2" t="s">
+        <v>2360</v>
+      </c>
+      <c r="J555" s="2" t="s">
+        <v>2416</v>
+      </c>
+      <c r="K555" s="2" t="s">
+        <v>2417</v>
+      </c>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="2" t="n">
         <v>555</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>2265</v>
+        <v>2418</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>2266</v>
+        <v>2419</v>
       </c>
       <c r="D556" s="2" t="s">
         <v>20</v>
@@ -26154,22 +27533,28 @@
         <v>1</v>
       </c>
       <c r="G556" s="2"/>
-      <c r="H556" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I556" s="2"/>
-      <c r="J556" s="2"/>
-      <c r="K556" s="2"/>
+      <c r="H556" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I556" s="2" t="s">
+        <v>2420</v>
+      </c>
+      <c r="J556" s="2" t="s">
+        <v>2421</v>
+      </c>
+      <c r="K556" s="2" t="s">
+        <v>2422</v>
+      </c>
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="2" t="n">
         <v>556</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>2267</v>
+        <v>2423</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>2268</v>
+        <v>2424</v>
       </c>
       <c r="D557" s="2" t="s">
         <v>20</v>
@@ -26181,19 +27566,25 @@
         <v>1</v>
       </c>
       <c r="G557" s="2"/>
-      <c r="H557" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I557" s="2"/>
-      <c r="J557" s="2"/>
-      <c r="K557" s="2"/>
+      <c r="H557" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I557" s="2" t="s">
+        <v>2425</v>
+      </c>
+      <c r="J557" s="2" t="s">
+        <v>2426</v>
+      </c>
+      <c r="K557" s="2" t="s">
+        <v>2427</v>
+      </c>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="2" t="n">
         <v>557</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>2269</v>
+        <v>2428</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>481</v>
@@ -26208,24 +27599,30 @@
         <v>1</v>
       </c>
       <c r="G558" s="2" t="s">
-        <v>2270</v>
-      </c>
-      <c r="H558" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I558" s="2"/>
-      <c r="J558" s="2"/>
-      <c r="K558" s="2"/>
+        <v>2429</v>
+      </c>
+      <c r="H558" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I558" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="J558" s="2" t="s">
+        <v>2430</v>
+      </c>
+      <c r="K558" s="2" t="s">
+        <v>2431</v>
+      </c>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="2" t="n">
         <v>558</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>2271</v>
+        <v>2432</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>2272</v>
+        <v>2433</v>
       </c>
       <c r="D559" s="2" t="s">
         <v>13</v>
@@ -26237,11 +27634,15 @@
         <v>1</v>
       </c>
       <c r="G559" s="2"/>
-      <c r="H559" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I559" s="2"/>
-      <c r="J559" s="2"/>
+      <c r="H559" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I559" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J559" s="2" t="s">
+        <v>2434</v>
+      </c>
       <c r="K559" s="2"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26249,10 +27650,10 @@
         <v>559</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>2271</v>
+        <v>2432</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>2273</v>
+        <v>2435</v>
       </c>
       <c r="D560" s="2" t="s">
         <v>61</v>
@@ -26264,24 +27665,30 @@
         <v>1</v>
       </c>
       <c r="G560" s="2" t="s">
-        <v>2274</v>
-      </c>
-      <c r="H560" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I560" s="2"/>
-      <c r="J560" s="2"/>
-      <c r="K560" s="2"/>
+        <v>2436</v>
+      </c>
+      <c r="H560" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I560" s="2" t="s">
+        <v>2437</v>
+      </c>
+      <c r="J560" s="2" t="s">
+        <v>2438</v>
+      </c>
+      <c r="K560" s="2" t="s">
+        <v>2439</v>
+      </c>
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="2" t="n">
         <v>560</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>2275</v>
+        <v>2440</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>2276</v>
+        <v>2441</v>
       </c>
       <c r="D561" s="2" t="s">
         <v>13</v>
@@ -26293,22 +27700,28 @@
         <v>1</v>
       </c>
       <c r="G561" s="2"/>
-      <c r="H561" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I561" s="2"/>
-      <c r="J561" s="2"/>
-      <c r="K561" s="2"/>
+      <c r="H561" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I561" s="2" t="s">
+        <v>2442</v>
+      </c>
+      <c r="J561" s="2" t="s">
+        <v>2443</v>
+      </c>
+      <c r="K561" s="2" t="s">
+        <v>2444</v>
+      </c>
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="2" t="n">
         <v>561</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>2277</v>
+        <v>2445</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>2278</v>
+        <v>2446</v>
       </c>
       <c r="D562" s="2" t="s">
         <v>20</v>
@@ -26320,19 +27733,25 @@
         <v>2</v>
       </c>
       <c r="G562" s="2"/>
-      <c r="H562" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I562" s="2"/>
-      <c r="J562" s="2"/>
-      <c r="K562" s="2"/>
+      <c r="H562" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I562" s="2" t="s">
+        <v>2447</v>
+      </c>
+      <c r="J562" s="2" t="s">
+        <v>2448</v>
+      </c>
+      <c r="K562" s="2" t="s">
+        <v>2449</v>
+      </c>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="2" t="n">
         <v>562</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>2279</v>
+        <v>2450</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>690</v>
@@ -26347,22 +27766,28 @@
         <v>1</v>
       </c>
       <c r="G563" s="2"/>
-      <c r="H563" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I563" s="2"/>
-      <c r="J563" s="2"/>
-      <c r="K563" s="2"/>
+      <c r="H563" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I563" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="J563" s="2" t="s">
+        <v>2452</v>
+      </c>
+      <c r="K563" s="2" t="s">
+        <v>2453</v>
+      </c>
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="2" t="n">
         <v>563</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>2280</v>
+        <v>2454</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>2281</v>
+        <v>2455</v>
       </c>
       <c r="D564" s="2" t="s">
         <v>42</v>
@@ -26374,13 +27799,17 @@
         <v>1</v>
       </c>
       <c r="G564" s="2" t="s">
-        <v>2282</v>
-      </c>
-      <c r="H564" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I564" s="2"/>
-      <c r="J564" s="2"/>
+        <v>2456</v>
+      </c>
+      <c r="H564" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I564" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J564" s="2" t="s">
+        <v>2457</v>
+      </c>
       <c r="K564" s="2"/>
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26388,10 +27817,10 @@
         <v>564</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>2283</v>
+        <v>2458</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>2284</v>
+        <v>2459</v>
       </c>
       <c r="D565" s="2" t="s">
         <v>13</v>
@@ -26403,19 +27832,25 @@
         <v>1</v>
       </c>
       <c r="G565" s="2"/>
-      <c r="H565" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I565" s="2"/>
-      <c r="J565" s="2"/>
-      <c r="K565" s="2"/>
+      <c r="H565" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I565" s="2" t="s">
+        <v>2460</v>
+      </c>
+      <c r="J565" s="2" t="s">
+        <v>2461</v>
+      </c>
+      <c r="K565" s="2" t="s">
+        <v>2462</v>
+      </c>
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="2" t="n">
         <v>565</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>2285</v>
+        <v>2463</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>690</v>
@@ -26430,14 +27865,20 @@
         <v>1</v>
       </c>
       <c r="G566" s="2" t="s">
-        <v>2286</v>
-      </c>
-      <c r="H566" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I566" s="2"/>
-      <c r="J566" s="2"/>
-      <c r="K566" s="2"/>
+        <v>2464</v>
+      </c>
+      <c r="H566" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I566" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J566" s="2" t="s">
+        <v>2465</v>
+      </c>
+      <c r="K566" s="2" t="s">
+        <v>2466</v>
+      </c>
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="2" t="n">
@@ -26447,7 +27888,7 @@
         <v>175</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>2287</v>
+        <v>2467</v>
       </c>
       <c r="D567" s="2" t="s">
         <v>61</v>
@@ -26459,13 +27900,13 @@
         <v>1</v>
       </c>
       <c r="G567" s="2" t="s">
-        <v>2288</v>
+        <v>2468</v>
       </c>
       <c r="H567" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I567" s="2" t="s">
-        <v>2289</v>
+        <v>2469</v>
       </c>
       <c r="J567" s="2" t="s">
         <v>47</v>
@@ -26477,7 +27918,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>2290</v>
+        <v>2470</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>319</v>
@@ -26492,24 +27933,30 @@
         <v>1</v>
       </c>
       <c r="G568" s="2" t="s">
-        <v>2291</v>
-      </c>
-      <c r="H568" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I568" s="2"/>
-      <c r="J568" s="2"/>
-      <c r="K568" s="2"/>
+        <v>2471</v>
+      </c>
+      <c r="H568" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I568" s="2" t="s">
+        <v>2472</v>
+      </c>
+      <c r="J568" s="2" t="s">
+        <v>2473</v>
+      </c>
+      <c r="K568" s="2" t="s">
+        <v>2474</v>
+      </c>
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="2" t="n">
         <v>568</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>2292</v>
+        <v>2475</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>2293</v>
+        <v>2476</v>
       </c>
       <c r="D569" s="2" t="s">
         <v>20</v>
@@ -26521,19 +27968,25 @@
         <v>1</v>
       </c>
       <c r="G569" s="2"/>
-      <c r="H569" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I569" s="2"/>
-      <c r="J569" s="2"/>
-      <c r="K569" s="2"/>
+      <c r="H569" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I569" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J569" s="2" t="s">
+        <v>2477</v>
+      </c>
+      <c r="K569" s="2" t="s">
+        <v>2478</v>
+      </c>
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="2" t="n">
         <v>569</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>2294</v>
+        <v>2479</v>
       </c>
       <c r="C570" s="2" t="s">
         <v>695</v>
@@ -26548,24 +28001,30 @@
         <v>2</v>
       </c>
       <c r="G570" s="2" t="s">
-        <v>2295</v>
-      </c>
-      <c r="H570" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I570" s="2"/>
-      <c r="J570" s="2"/>
-      <c r="K570" s="2"/>
+        <v>2480</v>
+      </c>
+      <c r="H570" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I570" s="2" t="s">
+        <v>2481</v>
+      </c>
+      <c r="J570" s="2" t="s">
+        <v>2482</v>
+      </c>
+      <c r="K570" s="2" t="s">
+        <v>2431</v>
+      </c>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="2" t="n">
         <v>570</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>2296</v>
+        <v>2483</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>2297</v>
+        <v>2484</v>
       </c>
       <c r="D571" s="2" t="s">
         <v>13</v>
@@ -26577,19 +28036,25 @@
         <v>1</v>
       </c>
       <c r="G571" s="2"/>
-      <c r="H571" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I571" s="2"/>
-      <c r="J571" s="2"/>
-      <c r="K571" s="2"/>
+      <c r="H571" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I571" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J571" s="2" t="s">
+        <v>2485</v>
+      </c>
+      <c r="K571" s="2" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="2" t="n">
         <v>571</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>2298</v>
+        <v>2487</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>968</v>
@@ -26604,22 +28069,28 @@
         <v>1</v>
       </c>
       <c r="G572" s="2"/>
-      <c r="H572" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I572" s="2"/>
-      <c r="J572" s="2"/>
-      <c r="K572" s="2"/>
+      <c r="H572" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I572" s="2" t="s">
+        <v>2488</v>
+      </c>
+      <c r="J572" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="K572" s="2" t="s">
+        <v>2490</v>
+      </c>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="2" t="n">
         <v>572</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>2299</v>
+        <v>2491</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>2300</v>
+        <v>2492</v>
       </c>
       <c r="D573" s="2" t="s">
         <v>98</v>
@@ -26631,22 +28102,28 @@
         <v>2</v>
       </c>
       <c r="G573" s="2"/>
-      <c r="H573" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I573" s="2"/>
-      <c r="J573" s="2"/>
-      <c r="K573" s="2"/>
+      <c r="H573" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I573" s="2" t="s">
+        <v>2493</v>
+      </c>
+      <c r="J573" s="2" t="s">
+        <v>2494</v>
+      </c>
+      <c r="K573" s="2" t="s">
+        <v>2495</v>
+      </c>
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="2" t="n">
         <v>573</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>2301</v>
+        <v>2496</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>2302</v>
+        <v>2497</v>
       </c>
       <c r="D574" s="2" t="s">
         <v>20</v>
@@ -26658,22 +28135,28 @@
         <v>1</v>
       </c>
       <c r="G574" s="2"/>
-      <c r="H574" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I574" s="2"/>
-      <c r="J574" s="2"/>
-      <c r="K574" s="2"/>
+      <c r="H574" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I574" s="2" t="s">
+        <v>2498</v>
+      </c>
+      <c r="J574" s="2" t="s">
+        <v>2499</v>
+      </c>
+      <c r="K574" s="2" t="s">
+        <v>2500</v>
+      </c>
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="2" t="n">
         <v>574</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>2303</v>
+        <v>2501</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>2304</v>
+        <v>2502</v>
       </c>
       <c r="D575" s="2" t="s">
         <v>13</v>
@@ -26685,22 +28168,28 @@
         <v>1</v>
       </c>
       <c r="G575" s="2"/>
-      <c r="H575" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I575" s="2"/>
-      <c r="J575" s="2"/>
-      <c r="K575" s="2"/>
+      <c r="H575" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I575" s="2" t="s">
+        <v>2503</v>
+      </c>
+      <c r="J575" s="2" t="s">
+        <v>2504</v>
+      </c>
+      <c r="K575" s="2" t="s">
+        <v>2505</v>
+      </c>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="2" t="n">
         <v>575</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>2305</v>
+        <v>2506</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>2306</v>
+        <v>2507</v>
       </c>
       <c r="D576" s="2" t="s">
         <v>20</v>
@@ -26712,19 +28201,25 @@
         <v>1</v>
       </c>
       <c r="G576" s="2"/>
-      <c r="H576" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I576" s="2"/>
-      <c r="J576" s="2"/>
-      <c r="K576" s="2"/>
+      <c r="H576" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I576" s="2" t="s">
+        <v>2508</v>
+      </c>
+      <c r="J576" s="2" t="s">
+        <v>2509</v>
+      </c>
+      <c r="K576" s="2" t="s">
+        <v>2510</v>
+      </c>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="2" t="n">
         <v>576</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>2307</v>
+        <v>2511</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>332</v>
@@ -26739,19 +28234,25 @@
         <v>1</v>
       </c>
       <c r="G577" s="2"/>
-      <c r="H577" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I577" s="2"/>
-      <c r="J577" s="2"/>
-      <c r="K577" s="2"/>
+      <c r="H577" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I577" s="2" t="s">
+        <v>2512</v>
+      </c>
+      <c r="J577" s="2" t="s">
+        <v>2513</v>
+      </c>
+      <c r="K577" s="2" t="s">
+        <v>2514</v>
+      </c>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="2" t="n">
         <v>577</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>2308</v>
+        <v>2515</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>157</v>
@@ -26766,19 +28267,25 @@
         <v>1</v>
       </c>
       <c r="G578" s="2"/>
-      <c r="H578" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I578" s="2"/>
-      <c r="J578" s="2"/>
-      <c r="K578" s="2"/>
+      <c r="H578" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I578" s="2" t="s">
+        <v>2516</v>
+      </c>
+      <c r="J578" s="2" t="s">
+        <v>2517</v>
+      </c>
+      <c r="K578" s="2" t="s">
+        <v>2518</v>
+      </c>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="2" t="n">
         <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>2309</v>
+        <v>2519</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>1365</v>
@@ -26793,24 +28300,30 @@
         <v>1</v>
       </c>
       <c r="G579" s="2" t="s">
-        <v>2310</v>
-      </c>
-      <c r="H579" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I579" s="2"/>
-      <c r="J579" s="2"/>
-      <c r="K579" s="2"/>
+        <v>2520</v>
+      </c>
+      <c r="H579" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I579" s="2" t="s">
+        <v>2521</v>
+      </c>
+      <c r="J579" s="2" t="s">
+        <v>2522</v>
+      </c>
+      <c r="K579" s="2" t="s">
+        <v>2523</v>
+      </c>
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="2" t="n">
         <v>579</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>2311</v>
+        <v>2524</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>2312</v>
+        <v>2525</v>
       </c>
       <c r="D580" s="2" t="s">
         <v>258</v>
@@ -26822,24 +28335,30 @@
         <v>3</v>
       </c>
       <c r="G580" s="2" t="s">
-        <v>2313</v>
-      </c>
-      <c r="H580" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I580" s="2"/>
-      <c r="J580" s="2"/>
-      <c r="K580" s="2"/>
+        <v>2526</v>
+      </c>
+      <c r="H580" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I580" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="J580" s="2" t="s">
+        <v>2527</v>
+      </c>
+      <c r="K580" s="2" t="s">
+        <v>2528</v>
+      </c>
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="2" t="n">
         <v>580</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>2314</v>
+        <v>2529</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>2315</v>
+        <v>2530</v>
       </c>
       <c r="D581" s="2" t="s">
         <v>98</v>
@@ -26851,22 +28370,28 @@
         <v>5</v>
       </c>
       <c r="G581" s="2"/>
-      <c r="H581" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I581" s="2"/>
-      <c r="J581" s="2"/>
-      <c r="K581" s="2"/>
+      <c r="H581" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I581" s="2" t="s">
+        <v>2531</v>
+      </c>
+      <c r="J581" s="2" t="s">
+        <v>2532</v>
+      </c>
+      <c r="K581" s="2" t="s">
+        <v>2533</v>
+      </c>
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="2" t="n">
         <v>581</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>2316</v>
+        <v>2534</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>2317</v>
+        <v>2535</v>
       </c>
       <c r="D582" s="2" t="s">
         <v>13</v>
@@ -26878,22 +28403,28 @@
         <v>1</v>
       </c>
       <c r="G582" s="2"/>
-      <c r="H582" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I582" s="2"/>
-      <c r="J582" s="2"/>
-      <c r="K582" s="2"/>
+      <c r="H582" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I582" s="2" t="s">
+        <v>2536</v>
+      </c>
+      <c r="J582" s="2" t="s">
+        <v>2537</v>
+      </c>
+      <c r="K582" s="2" t="s">
+        <v>2538</v>
+      </c>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="2" t="n">
         <v>582</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>2318</v>
+        <v>2539</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>2319</v>
+        <v>2540</v>
       </c>
       <c r="D583" s="2" t="s">
         <v>61</v>
@@ -26905,27 +28436,33 @@
         <v>1</v>
       </c>
       <c r="G583" s="2" t="s">
-        <v>2320</v>
-      </c>
-      <c r="H583" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I583" s="2"/>
-      <c r="J583" s="2"/>
-      <c r="K583" s="2"/>
+        <v>2541</v>
+      </c>
+      <c r="H583" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I583" s="2" t="s">
+        <v>2542</v>
+      </c>
+      <c r="J583" s="2" t="s">
+        <v>2543</v>
+      </c>
+      <c r="K583" s="2" t="s">
+        <v>2544</v>
+      </c>
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="2" t="n">
         <v>583</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>2321</v>
+        <v>2545</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>2322</v>
+        <v>2546</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>2323</v>
+        <v>2547</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>182</v>
@@ -26934,21 +28471,27 @@
         <v>3</v>
       </c>
       <c r="G584" s="2" t="s">
-        <v>2324</v>
-      </c>
-      <c r="H584" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I584" s="2"/>
-      <c r="J584" s="2"/>
-      <c r="K584" s="2"/>
+        <v>2548</v>
+      </c>
+      <c r="H584" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I584" s="2" t="s">
+        <v>2549</v>
+      </c>
+      <c r="J584" s="2" t="s">
+        <v>2550</v>
+      </c>
+      <c r="K584" s="2" t="s">
+        <v>2551</v>
+      </c>
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="2" t="n">
         <v>584</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>2325</v>
+        <v>2552</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>251</v>
@@ -26963,22 +28506,28 @@
         <v>2</v>
       </c>
       <c r="G585" s="2"/>
-      <c r="H585" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I585" s="2"/>
-      <c r="J585" s="2"/>
-      <c r="K585" s="2"/>
+      <c r="H585" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I585" s="2" t="s">
+        <v>2553</v>
+      </c>
+      <c r="J585" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="K585" s="2" t="s">
+        <v>2555</v>
+      </c>
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="2" t="n">
         <v>585</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>2326</v>
+        <v>2556</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>2327</v>
+        <v>2557</v>
       </c>
       <c r="D586" s="2" t="s">
         <v>61</v>
@@ -26990,24 +28539,30 @@
         <v>1</v>
       </c>
       <c r="G586" s="2" t="s">
-        <v>2328</v>
-      </c>
-      <c r="H586" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I586" s="2"/>
-      <c r="J586" s="2"/>
-      <c r="K586" s="2"/>
+        <v>2558</v>
+      </c>
+      <c r="H586" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I586" s="2" t="s">
+        <v>2559</v>
+      </c>
+      <c r="J586" s="2" t="s">
+        <v>2560</v>
+      </c>
+      <c r="K586" s="2" t="s">
+        <v>2561</v>
+      </c>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="2" t="n">
         <v>586</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>2326</v>
+        <v>2556</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>2329</v>
+        <v>2562</v>
       </c>
       <c r="D587" s="2" t="s">
         <v>13</v>
@@ -27019,11 +28574,15 @@
         <v>1</v>
       </c>
       <c r="G587" s="2"/>
-      <c r="H587" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I587" s="2"/>
-      <c r="J587" s="2"/>
+      <c r="H587" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I587" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J587" s="2" t="s">
+        <v>2563</v>
+      </c>
       <c r="K587" s="2"/>
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27031,10 +28590,10 @@
         <v>587</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>2326</v>
+        <v>2556</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>2330</v>
+        <v>2564</v>
       </c>
       <c r="D588" s="2" t="s">
         <v>258</v>
@@ -27046,24 +28605,30 @@
         <v>4</v>
       </c>
       <c r="G588" s="2" t="s">
-        <v>2331</v>
-      </c>
-      <c r="H588" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I588" s="2"/>
-      <c r="J588" s="2"/>
-      <c r="K588" s="2"/>
+        <v>2565</v>
+      </c>
+      <c r="H588" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I588" s="2" t="s">
+        <v>2566</v>
+      </c>
+      <c r="J588" s="2" t="s">
+        <v>2567</v>
+      </c>
+      <c r="K588" s="2" t="s">
+        <v>2568</v>
+      </c>
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="2" t="n">
         <v>588</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>2326</v>
+        <v>2556</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>2332</v>
+        <v>2569</v>
       </c>
       <c r="D589" s="2" t="s">
         <v>61</v>
@@ -27075,24 +28640,30 @@
         <v>1</v>
       </c>
       <c r="G589" s="2" t="s">
-        <v>2333</v>
-      </c>
-      <c r="H589" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I589" s="2"/>
-      <c r="J589" s="2"/>
-      <c r="K589" s="2"/>
+        <v>2570</v>
+      </c>
+      <c r="H589" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I589" s="2" t="s">
+        <v>2571</v>
+      </c>
+      <c r="J589" s="2" t="s">
+        <v>2572</v>
+      </c>
+      <c r="K589" s="2" t="s">
+        <v>2573</v>
+      </c>
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="2" t="n">
         <v>589</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>2334</v>
+        <v>2574</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>2335</v>
+        <v>2575</v>
       </c>
       <c r="D590" s="2" t="s">
         <v>13</v>
@@ -27104,19 +28675,25 @@
         <v>1</v>
       </c>
       <c r="G590" s="2"/>
-      <c r="H590" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I590" s="2"/>
-      <c r="J590" s="2"/>
-      <c r="K590" s="2"/>
+      <c r="H590" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I590" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J590" s="2" t="s">
+        <v>2576</v>
+      </c>
+      <c r="K590" s="2" t="s">
+        <v>2577</v>
+      </c>
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="2" t="n">
         <v>590</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>2336</v>
+        <v>2578</v>
       </c>
       <c r="C591" s="2" t="s">
         <v>1040</v>
@@ -27131,22 +28708,28 @@
         <v>1</v>
       </c>
       <c r="G591" s="2"/>
-      <c r="H591" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I591" s="2"/>
-      <c r="J591" s="2"/>
-      <c r="K591" s="2"/>
+      <c r="H591" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I591" s="2" t="s">
+        <v>2579</v>
+      </c>
+      <c r="J591" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="K591" s="2" t="s">
+        <v>2581</v>
+      </c>
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="2" t="n">
         <v>591</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>2337</v>
+        <v>2582</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>2338</v>
+        <v>2583</v>
       </c>
       <c r="D592" s="2" t="s">
         <v>13</v>
@@ -27158,19 +28741,25 @@
         <v>1</v>
       </c>
       <c r="G592" s="2"/>
-      <c r="H592" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I592" s="2"/>
-      <c r="J592" s="2"/>
-      <c r="K592" s="2"/>
+      <c r="H592" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I592" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="J592" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="K592" s="2" t="s">
+        <v>2586</v>
+      </c>
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="2" t="n">
         <v>592</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>2339</v>
+        <v>2587</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>505</v>
@@ -27185,24 +28774,30 @@
         <v>1</v>
       </c>
       <c r="G593" s="2" t="s">
-        <v>2340</v>
-      </c>
-      <c r="H593" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I593" s="2"/>
-      <c r="J593" s="2"/>
-      <c r="K593" s="2"/>
+        <v>2588</v>
+      </c>
+      <c r="H593" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I593" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J593" s="2" t="s">
+        <v>2589</v>
+      </c>
+      <c r="K593" s="2" t="s">
+        <v>2590</v>
+      </c>
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="2" t="n">
         <v>593</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>2341</v>
+        <v>2591</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>2342</v>
+        <v>2592</v>
       </c>
       <c r="D594" s="2" t="s">
         <v>42</v>
@@ -27214,24 +28809,30 @@
         <v>1</v>
       </c>
       <c r="G594" s="2" t="s">
-        <v>2343</v>
-      </c>
-      <c r="H594" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I594" s="2"/>
-      <c r="J594" s="2"/>
-      <c r="K594" s="2"/>
+        <v>2593</v>
+      </c>
+      <c r="H594" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I594" s="2" t="s">
+        <v>2594</v>
+      </c>
+      <c r="J594" s="2" t="s">
+        <v>2595</v>
+      </c>
+      <c r="K594" s="2" t="s">
+        <v>2596</v>
+      </c>
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="2" t="n">
         <v>594</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>2341</v>
+        <v>2591</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>2344</v>
+        <v>2597</v>
       </c>
       <c r="D595" s="2" t="s">
         <v>42</v>
@@ -27243,24 +28844,30 @@
         <v>1</v>
       </c>
       <c r="G595" s="2" t="s">
-        <v>2345</v>
-      </c>
-      <c r="H595" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I595" s="2"/>
-      <c r="J595" s="2"/>
-      <c r="K595" s="2"/>
+        <v>2598</v>
+      </c>
+      <c r="H595" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I595" s="2" t="s">
+        <v>2599</v>
+      </c>
+      <c r="J595" s="2" t="s">
+        <v>2600</v>
+      </c>
+      <c r="K595" s="2" t="s">
+        <v>2601</v>
+      </c>
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="2" t="n">
         <v>595</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>2341</v>
+        <v>2591</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>2346</v>
+        <v>2602</v>
       </c>
       <c r="D596" s="2" t="s">
         <v>61</v>
@@ -27272,24 +28879,30 @@
         <v>1</v>
       </c>
       <c r="G596" s="2" t="s">
-        <v>2347</v>
-      </c>
-      <c r="H596" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I596" s="2"/>
-      <c r="J596" s="2"/>
-      <c r="K596" s="2"/>
+        <v>2603</v>
+      </c>
+      <c r="H596" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I596" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J596" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="K596" s="2" t="s">
+        <v>2605</v>
+      </c>
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="2" t="n">
         <v>596</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>2348</v>
+        <v>2606</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>2349</v>
+        <v>2607</v>
       </c>
       <c r="D597" s="2" t="s">
         <v>13</v>
@@ -27301,22 +28914,28 @@
         <v>2</v>
       </c>
       <c r="G597" s="2"/>
-      <c r="H597" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I597" s="2"/>
-      <c r="J597" s="2"/>
-      <c r="K597" s="2"/>
+      <c r="H597" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I597" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="J597" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="K597" s="2" t="s">
+        <v>2610</v>
+      </c>
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="2" t="n">
         <v>597</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>2350</v>
+        <v>2611</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>2351</v>
+        <v>2612</v>
       </c>
       <c r="D598" s="2" t="s">
         <v>13</v>
@@ -27328,22 +28947,28 @@
         <v>1</v>
       </c>
       <c r="G598" s="2"/>
-      <c r="H598" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I598" s="2"/>
-      <c r="J598" s="2"/>
-      <c r="K598" s="2"/>
+      <c r="H598" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I598" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J598" s="2" t="s">
+        <v>2613</v>
+      </c>
+      <c r="K598" s="2" t="s">
+        <v>2614</v>
+      </c>
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="2" t="n">
         <v>598</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>2352</v>
+        <v>2615</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>2103</v>
+        <v>2146</v>
       </c>
       <c r="D599" s="2" t="s">
         <v>13</v>
@@ -27355,11 +28980,15 @@
         <v>1</v>
       </c>
       <c r="G599" s="2"/>
-      <c r="H599" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I599" s="2"/>
-      <c r="J599" s="2"/>
+      <c r="H599" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I599" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J599" s="2" t="s">
+        <v>2616</v>
+      </c>
       <c r="K599" s="2"/>
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27367,7 +28996,7 @@
         <v>599</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>2353</v>
+        <v>2617</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>272</v>
@@ -27389,10 +29018,10 @@
         <v>22</v>
       </c>
       <c r="J600" s="2" t="s">
-        <v>2354</v>
+        <v>2618</v>
       </c>
       <c r="K600" s="2" t="s">
-        <v>2355</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27400,10 +29029,10 @@
         <v>600</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>2356</v>
+        <v>2620</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>2357</v>
+        <v>2621</v>
       </c>
       <c r="D601" s="2" t="s">
         <v>42</v>
@@ -27415,7 +29044,7 @@
         <v>1</v>
       </c>
       <c r="G601" s="2" t="s">
-        <v>2358</v>
+        <v>2622</v>
       </c>
       <c r="H601" s="4" t="s">
         <v>21</v>
@@ -27424,10 +29053,10 @@
         <v>288</v>
       </c>
       <c r="J601" s="2" t="s">
-        <v>2359</v>
+        <v>2623</v>
       </c>
       <c r="K601" s="2" t="s">
-        <v>2360</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27435,7 +29064,7 @@
         <v>601</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>2361</v>
+        <v>2625</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>356</v>
@@ -27450,19 +29079,19 @@
         <v>1</v>
       </c>
       <c r="G602" s="2" t="s">
-        <v>2362</v>
+        <v>2626</v>
       </c>
       <c r="H602" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I602" s="2" t="s">
-        <v>2363</v>
+        <v>2627</v>
       </c>
       <c r="J602" s="2" t="s">
-        <v>2364</v>
+        <v>2628</v>
       </c>
       <c r="K602" s="2" t="s">
-        <v>2365</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27470,10 +29099,10 @@
         <v>602</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>2366</v>
+        <v>2630</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>2367</v>
+        <v>2631</v>
       </c>
       <c r="D603" s="2" t="s">
         <v>98</v>
@@ -27489,13 +29118,13 @@
         <v>21</v>
       </c>
       <c r="I603" s="2" t="s">
-        <v>2368</v>
+        <v>2632</v>
       </c>
       <c r="J603" s="2" t="s">
-        <v>2369</v>
+        <v>2633</v>
       </c>
       <c r="K603" s="2" t="s">
-        <v>2370</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27503,10 +29132,10 @@
         <v>603</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>2371</v>
+        <v>2635</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>2107</v>
+        <v>2153</v>
       </c>
       <c r="D604" s="2" t="s">
         <v>13</v>
@@ -27525,10 +29154,10 @@
         <v>528</v>
       </c>
       <c r="J604" s="2" t="s">
-        <v>2372</v>
+        <v>2636</v>
       </c>
       <c r="K604" s="2" t="s">
-        <v>2373</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27536,7 +29165,7 @@
         <v>604</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>2374</v>
+        <v>2638</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>359</v>
@@ -27558,10 +29187,10 @@
         <v>619</v>
       </c>
       <c r="J605" s="2" t="s">
-        <v>2375</v>
+        <v>2639</v>
       </c>
       <c r="K605" s="2" t="s">
-        <v>2376</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27569,7 +29198,7 @@
         <v>605</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>2377</v>
+        <v>2641</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>337</v>
@@ -27588,13 +29217,13 @@
         <v>15</v>
       </c>
       <c r="I606" s="2" t="s">
-        <v>2378</v>
+        <v>2642</v>
       </c>
       <c r="J606" s="2" t="s">
-        <v>2379</v>
+        <v>2643</v>
       </c>
       <c r="K606" s="2" t="s">
-        <v>2380</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27602,10 +29231,10 @@
         <v>606</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>2381</v>
+        <v>2644</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>2382</v>
+        <v>2645</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>13</v>
@@ -27621,13 +29250,13 @@
         <v>21</v>
       </c>
       <c r="I607" s="2" t="s">
-        <v>2383</v>
+        <v>2646</v>
       </c>
       <c r="J607" s="2" t="s">
-        <v>2384</v>
+        <v>2647</v>
       </c>
       <c r="K607" s="2" t="s">
-        <v>2385</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27635,10 +29264,10 @@
         <v>607</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>2386</v>
+        <v>2649</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>2387</v>
+        <v>2650</v>
       </c>
       <c r="D608" s="2" t="s">
         <v>13</v>
@@ -27654,13 +29283,13 @@
         <v>15</v>
       </c>
       <c r="I608" s="2" t="s">
-        <v>2388</v>
+        <v>2651</v>
       </c>
       <c r="J608" s="2" t="s">
-        <v>2389</v>
+        <v>2652</v>
       </c>
       <c r="K608" s="2" t="s">
-        <v>2390</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27668,10 +29297,10 @@
         <v>608</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>2391</v>
+        <v>2654</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>2392</v>
+        <v>2655</v>
       </c>
       <c r="D609" s="2" t="s">
         <v>13</v>
@@ -27687,13 +29316,13 @@
         <v>21</v>
       </c>
       <c r="I609" s="2" t="s">
-        <v>2249</v>
+        <v>2400</v>
       </c>
       <c r="J609" s="2" t="s">
-        <v>2393</v>
+        <v>2656</v>
       </c>
       <c r="K609" s="2" t="s">
-        <v>2394</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27701,10 +29330,10 @@
         <v>609</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>2391</v>
+        <v>2654</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>2395</v>
+        <v>2658</v>
       </c>
       <c r="D610" s="2" t="s">
         <v>13</v>
@@ -27720,13 +29349,13 @@
         <v>21</v>
       </c>
       <c r="I610" s="2" t="s">
-        <v>2396</v>
+        <v>2659</v>
       </c>
       <c r="J610" s="2" t="s">
-        <v>2397</v>
+        <v>2660</v>
       </c>
       <c r="K610" s="2" t="s">
-        <v>2398</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27734,10 +29363,10 @@
         <v>610</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>2399</v>
+        <v>2662</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>2400</v>
+        <v>2663</v>
       </c>
       <c r="D611" s="2" t="s">
         <v>13</v>
@@ -27753,13 +29382,13 @@
         <v>15</v>
       </c>
       <c r="I611" s="2" t="s">
-        <v>2401</v>
+        <v>2664</v>
       </c>
       <c r="J611" s="2" t="s">
-        <v>2402</v>
+        <v>2665</v>
       </c>
       <c r="K611" s="2" t="s">
-        <v>2403</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27767,10 +29396,10 @@
         <v>611</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>2404</v>
+        <v>2667</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>2405</v>
+        <v>2668</v>
       </c>
       <c r="D612" s="2" t="s">
         <v>61</v>
@@ -27782,7 +29411,7 @@
         <v>1</v>
       </c>
       <c r="G612" s="2" t="s">
-        <v>2406</v>
+        <v>2669</v>
       </c>
       <c r="H612" s="4" t="s">
         <v>21</v>
@@ -27791,10 +29420,10 @@
         <v>1968</v>
       </c>
       <c r="J612" s="2" t="s">
-        <v>2407</v>
+        <v>2670</v>
       </c>
       <c r="K612" s="2" t="s">
-        <v>2408</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27802,10 +29431,10 @@
         <v>612</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>2409</v>
+        <v>2672</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>2410</v>
+        <v>2673</v>
       </c>
       <c r="D613" s="2" t="s">
         <v>13</v>
@@ -27821,13 +29450,13 @@
         <v>21</v>
       </c>
       <c r="I613" s="2" t="s">
-        <v>2411</v>
+        <v>2674</v>
       </c>
       <c r="J613" s="2" t="s">
-        <v>2412</v>
+        <v>2675</v>
       </c>
       <c r="K613" s="2" t="s">
-        <v>2413</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27835,10 +29464,10 @@
         <v>613</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>2414</v>
+        <v>2677</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>2240</v>
+        <v>2391</v>
       </c>
       <c r="D614" s="2" t="s">
         <v>13</v>
@@ -27850,22 +29479,28 @@
         <v>1</v>
       </c>
       <c r="G614" s="2"/>
-      <c r="H614" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I614" s="2"/>
-      <c r="J614" s="2"/>
-      <c r="K614" s="2"/>
+      <c r="H614" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I614" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J614" s="2" t="s">
+        <v>2678</v>
+      </c>
+      <c r="K614" s="2" t="s">
+        <v>2679</v>
+      </c>
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="2" t="n">
         <v>614</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>2414</v>
+        <v>2677</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>2415</v>
+        <v>2680</v>
       </c>
       <c r="D615" s="2" t="s">
         <v>61</v>
@@ -27877,24 +29512,30 @@
         <v>1</v>
       </c>
       <c r="G615" s="2" t="s">
-        <v>2416</v>
-      </c>
-      <c r="H615" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I615" s="2"/>
-      <c r="J615" s="2"/>
-      <c r="K615" s="2"/>
+        <v>2681</v>
+      </c>
+      <c r="H615" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I615" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J615" s="2" t="s">
+        <v>2682</v>
+      </c>
+      <c r="K615" s="2" t="s">
+        <v>2683</v>
+      </c>
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="2" t="n">
         <v>615</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>2414</v>
+        <v>2677</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>2417</v>
+        <v>2684</v>
       </c>
       <c r="D616" s="2" t="s">
         <v>61</v>
@@ -27906,24 +29547,30 @@
         <v>1</v>
       </c>
       <c r="G616" s="2" t="s">
-        <v>2418</v>
-      </c>
-      <c r="H616" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I616" s="2"/>
-      <c r="J616" s="2"/>
-      <c r="K616" s="2"/>
+        <v>2685</v>
+      </c>
+      <c r="H616" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I616" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="J616" s="2" t="s">
+        <v>2686</v>
+      </c>
+      <c r="K616" s="2" t="s">
+        <v>2687</v>
+      </c>
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="2" t="n">
         <v>616</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>2414</v>
+        <v>2677</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>2419</v>
+        <v>2688</v>
       </c>
       <c r="D617" s="2" t="s">
         <v>13</v>
@@ -27935,22 +29582,28 @@
         <v>1</v>
       </c>
       <c r="G617" s="2"/>
-      <c r="H617" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I617" s="2"/>
-      <c r="J617" s="2"/>
-      <c r="K617" s="2"/>
+      <c r="H617" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I617" s="2" t="s">
+        <v>2689</v>
+      </c>
+      <c r="J617" s="2" t="s">
+        <v>2690</v>
+      </c>
+      <c r="K617" s="2" t="s">
+        <v>2691</v>
+      </c>
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="2" t="n">
         <v>617</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>2414</v>
+        <v>2677</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>2420</v>
+        <v>2692</v>
       </c>
       <c r="D618" s="2" t="s">
         <v>98</v>
@@ -27962,22 +29615,28 @@
         <v>2</v>
       </c>
       <c r="G618" s="2"/>
-      <c r="H618" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I618" s="2"/>
-      <c r="J618" s="2"/>
-      <c r="K618" s="2"/>
+      <c r="H618" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I618" s="2" t="s">
+        <v>2693</v>
+      </c>
+      <c r="J618" s="2" t="s">
+        <v>2694</v>
+      </c>
+      <c r="K618" s="2" t="s">
+        <v>2695</v>
+      </c>
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="2" t="n">
         <v>618</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>2421</v>
+        <v>2696</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>2422</v>
+        <v>2697</v>
       </c>
       <c r="D619" s="2" t="s">
         <v>13</v>
@@ -27989,22 +29648,28 @@
         <v>1</v>
       </c>
       <c r="G619" s="2"/>
-      <c r="H619" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I619" s="2"/>
-      <c r="J619" s="2"/>
-      <c r="K619" s="2"/>
+      <c r="H619" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I619" s="2" t="s">
+        <v>2698</v>
+      </c>
+      <c r="J619" s="2" t="s">
+        <v>2699</v>
+      </c>
+      <c r="K619" s="2" t="s">
+        <v>2700</v>
+      </c>
     </row>
     <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="2" t="n">
         <v>619</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>2423</v>
+        <v>2701</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>2391</v>
+        <v>2654</v>
       </c>
       <c r="D620" s="2" t="s">
         <v>61</v>
@@ -28016,13 +29681,17 @@
         <v>1</v>
       </c>
       <c r="G620" s="2" t="s">
-        <v>2424</v>
-      </c>
-      <c r="H620" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I620" s="2"/>
-      <c r="J620" s="2"/>
+        <v>2702</v>
+      </c>
+      <c r="H620" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I620" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="J620" s="2" t="s">
+        <v>2703</v>
+      </c>
       <c r="K620" s="2"/>
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28033,7 +29702,7 @@
         <v>2033</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>2425</v>
+        <v>2704</v>
       </c>
       <c r="D621" s="2" t="s">
         <v>20</v>
@@ -28045,12 +29714,18 @@
         <v>1</v>
       </c>
       <c r="G621" s="2"/>
-      <c r="H621" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I621" s="2"/>
-      <c r="J621" s="2"/>
-      <c r="K621" s="2"/>
+      <c r="H621" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I621" s="2" t="s">
+        <v>2705</v>
+      </c>
+      <c r="J621" s="2" t="s">
+        <v>2706</v>
+      </c>
+      <c r="K621" s="2" t="s">
+        <v>2707</v>
+      </c>
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="2" t="n">
@@ -28060,7 +29735,7 @@
         <v>1722</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>2426</v>
+        <v>2708</v>
       </c>
       <c r="D622" s="2" t="s">
         <v>61</v>
@@ -28072,27 +29747,33 @@
         <v>1</v>
       </c>
       <c r="G622" s="2" t="s">
-        <v>2427</v>
-      </c>
-      <c r="H622" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I622" s="2"/>
-      <c r="J622" s="2"/>
-      <c r="K622" s="2"/>
+        <v>2709</v>
+      </c>
+      <c r="H622" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I622" s="2" t="s">
+        <v>2710</v>
+      </c>
+      <c r="J622" s="2" t="s">
+        <v>2711</v>
+      </c>
+      <c r="K622" s="2" t="s">
+        <v>2712</v>
+      </c>
     </row>
     <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="2" t="n">
         <v>622</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>2428</v>
+        <v>2713</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>2429</v>
+        <v>2714</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>2430</v>
+        <v>2715</v>
       </c>
       <c r="E623" s="2" t="s">
         <v>182</v>
@@ -28101,24 +29782,30 @@
         <v>3</v>
       </c>
       <c r="G623" s="2" t="s">
-        <v>2431</v>
-      </c>
-      <c r="H623" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I623" s="2"/>
-      <c r="J623" s="2"/>
-      <c r="K623" s="2"/>
+        <v>2716</v>
+      </c>
+      <c r="H623" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I623" s="2" t="s">
+        <v>2717</v>
+      </c>
+      <c r="J623" s="2" t="s">
+        <v>2718</v>
+      </c>
+      <c r="K623" s="2" t="s">
+        <v>2719</v>
+      </c>
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="2" t="n">
         <v>623</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>2432</v>
+        <v>2720</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>2433</v>
+        <v>2721</v>
       </c>
       <c r="D624" s="2" t="s">
         <v>13</v>
@@ -28130,22 +29817,28 @@
         <v>1</v>
       </c>
       <c r="G624" s="2"/>
-      <c r="H624" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I624" s="2"/>
-      <c r="J624" s="2"/>
-      <c r="K624" s="2"/>
+      <c r="H624" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I624" s="2" t="s">
+        <v>2722</v>
+      </c>
+      <c r="J624" s="2" t="s">
+        <v>2723</v>
+      </c>
+      <c r="K624" s="2" t="s">
+        <v>2724</v>
+      </c>
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="2" t="n">
         <v>624</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>2434</v>
+        <v>2725</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>2435</v>
+        <v>2726</v>
       </c>
       <c r="D625" s="2" t="s">
         <v>61</v>
@@ -28157,21 +29850,27 @@
         <v>2</v>
       </c>
       <c r="G625" s="2" t="s">
-        <v>2436</v>
-      </c>
-      <c r="H625" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I625" s="2"/>
-      <c r="J625" s="2"/>
-      <c r="K625" s="2"/>
+        <v>2727</v>
+      </c>
+      <c r="H625" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I625" s="2" t="s">
+        <v>2728</v>
+      </c>
+      <c r="J625" s="2" t="s">
+        <v>2729</v>
+      </c>
+      <c r="K625" s="2" t="s">
+        <v>2730</v>
+      </c>
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="2" t="n">
         <v>625</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>2437</v>
+        <v>2731</v>
       </c>
       <c r="C626" s="2" t="s">
         <v>351</v>
@@ -28186,22 +29885,28 @@
         <v>1</v>
       </c>
       <c r="G626" s="2"/>
-      <c r="H626" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I626" s="2"/>
-      <c r="J626" s="2"/>
-      <c r="K626" s="2"/>
+      <c r="H626" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I626" s="2" t="s">
+        <v>2732</v>
+      </c>
+      <c r="J626" s="2" t="s">
+        <v>2733</v>
+      </c>
+      <c r="K626" s="2" t="s">
+        <v>2734</v>
+      </c>
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="2" t="n">
         <v>626</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>2438</v>
+        <v>2735</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>2439</v>
+        <v>2736</v>
       </c>
       <c r="D627" s="2" t="s">
         <v>20</v>
@@ -28213,19 +29918,25 @@
         <v>1</v>
       </c>
       <c r="G627" s="2"/>
-      <c r="H627" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I627" s="2"/>
-      <c r="J627" s="2"/>
-      <c r="K627" s="2"/>
+      <c r="H627" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I627" s="2" t="s">
+        <v>2737</v>
+      </c>
+      <c r="J627" s="2" t="s">
+        <v>2738</v>
+      </c>
+      <c r="K627" s="2" t="s">
+        <v>2739</v>
+      </c>
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="2" t="n">
         <v>627</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>2440</v>
+        <v>2740</v>
       </c>
       <c r="C628" s="2" t="s">
         <v>1089</v>
@@ -28240,11 +29951,15 @@
         <v>1</v>
       </c>
       <c r="G628" s="2"/>
-      <c r="H628" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I628" s="2"/>
-      <c r="J628" s="2"/>
+      <c r="H628" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I628" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J628" s="2" t="s">
+        <v>2741</v>
+      </c>
       <c r="K628" s="2"/>
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28252,13 +29967,13 @@
         <v>628</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>2441</v>
+        <v>2742</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>2442</v>
+        <v>2743</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>2323</v>
+        <v>2547</v>
       </c>
       <c r="E629" s="2" t="s">
         <v>182</v>
@@ -28267,27 +29982,33 @@
         <v>10</v>
       </c>
       <c r="G629" s="2" t="s">
-        <v>2443</v>
-      </c>
-      <c r="H629" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I629" s="2"/>
-      <c r="J629" s="2"/>
-      <c r="K629" s="2"/>
+        <v>2744</v>
+      </c>
+      <c r="H629" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I629" s="2" t="s">
+        <v>2745</v>
+      </c>
+      <c r="J629" s="2" t="s">
+        <v>2746</v>
+      </c>
+      <c r="K629" s="2" t="s">
+        <v>2747</v>
+      </c>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="2" t="n">
         <v>629</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>2441</v>
+        <v>2742</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>2444</v>
+        <v>2748</v>
       </c>
       <c r="D630" s="2" t="s">
-        <v>2323</v>
+        <v>2547</v>
       </c>
       <c r="E630" s="2" t="s">
         <v>182</v>
@@ -28296,24 +30017,30 @@
         <v>3</v>
       </c>
       <c r="G630" s="2" t="s">
-        <v>2445</v>
-      </c>
-      <c r="H630" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I630" s="2"/>
-      <c r="J630" s="2"/>
-      <c r="K630" s="2"/>
+        <v>2749</v>
+      </c>
+      <c r="H630" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I630" s="2" t="s">
+        <v>2750</v>
+      </c>
+      <c r="J630" s="2" t="s">
+        <v>2751</v>
+      </c>
+      <c r="K630" s="2" t="s">
+        <v>2752</v>
+      </c>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="2" t="n">
         <v>630</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>2441</v>
+        <v>2742</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>2446</v>
+        <v>2753</v>
       </c>
       <c r="D631" s="2" t="s">
         <v>258</v>
@@ -28325,24 +30052,30 @@
         <v>2</v>
       </c>
       <c r="G631" s="2" t="s">
-        <v>2447</v>
-      </c>
-      <c r="H631" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I631" s="2"/>
-      <c r="J631" s="2"/>
-      <c r="K631" s="2"/>
+        <v>2754</v>
+      </c>
+      <c r="H631" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I631" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="J631" s="2" t="s">
+        <v>2755</v>
+      </c>
+      <c r="K631" s="2" t="s">
+        <v>2756</v>
+      </c>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="2" t="n">
         <v>631</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>2441</v>
+        <v>2742</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>2448</v>
+        <v>2757</v>
       </c>
       <c r="D632" s="2" t="s">
         <v>13</v>
@@ -28354,11 +30087,15 @@
         <v>1</v>
       </c>
       <c r="G632" s="2"/>
-      <c r="H632" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I632" s="2"/>
-      <c r="J632" s="2"/>
+      <c r="H632" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I632" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J632" s="2" t="s">
+        <v>2758</v>
+      </c>
       <c r="K632" s="2"/>
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28366,10 +30103,10 @@
         <v>632</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>2441</v>
+        <v>2742</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>2449</v>
+        <v>2759</v>
       </c>
       <c r="D633" s="2" t="s">
         <v>42</v>
@@ -28381,13 +30118,13 @@
         <v>1</v>
       </c>
       <c r="G633" s="2" t="s">
-        <v>2450</v>
+        <v>2760</v>
       </c>
       <c r="H633" s="5" t="s">
         <v>45</v>
       </c>
       <c r="I633" s="2" t="s">
-        <v>2451</v>
+        <v>2761</v>
       </c>
       <c r="J633" s="2" t="s">
         <v>47</v>
@@ -28399,10 +30136,10 @@
         <v>633</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>2452</v>
+        <v>2762</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>2453</v>
+        <v>2763</v>
       </c>
       <c r="D634" s="2" t="s">
         <v>13</v>
@@ -28414,11 +30151,15 @@
         <v>1</v>
       </c>
       <c r="G634" s="2"/>
-      <c r="H634" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I634" s="2"/>
-      <c r="J634" s="2"/>
+      <c r="H634" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I634" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J634" s="2" t="s">
+        <v>2764</v>
+      </c>
       <c r="K634" s="2"/>
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28426,10 +30167,10 @@
         <v>634</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>2452</v>
+        <v>2762</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>2454</v>
+        <v>2765</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>20</v>
@@ -28441,11 +30182,15 @@
         <v>1</v>
       </c>
       <c r="G635" s="2"/>
-      <c r="H635" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I635" s="2"/>
-      <c r="J635" s="2"/>
+      <c r="H635" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I635" s="2" t="s">
+        <v>2766</v>
+      </c>
+      <c r="J635" s="2" t="s">
+        <v>2767</v>
+      </c>
       <c r="K635" s="2"/>
     </row>
     <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28453,7 +30198,7 @@
         <v>635</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>2455</v>
+        <v>2768</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>1236</v>
@@ -28468,24 +30213,30 @@
         <v>2</v>
       </c>
       <c r="G636" s="2" t="s">
-        <v>2456</v>
-      </c>
-      <c r="H636" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I636" s="2"/>
-      <c r="J636" s="2"/>
-      <c r="K636" s="2"/>
+        <v>2769</v>
+      </c>
+      <c r="H636" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I636" s="2" t="s">
+        <v>2770</v>
+      </c>
+      <c r="J636" s="2" t="s">
+        <v>2771</v>
+      </c>
+      <c r="K636" s="2" t="s">
+        <v>2772</v>
+      </c>
     </row>
     <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="2" t="n">
         <v>636</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>2457</v>
+        <v>2773</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>2458</v>
+        <v>2774</v>
       </c>
       <c r="D637" s="2" t="s">
         <v>13</v>
@@ -28497,22 +30248,28 @@
         <v>1</v>
       </c>
       <c r="G637" s="2"/>
-      <c r="H637" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I637" s="2"/>
-      <c r="J637" s="2"/>
-      <c r="K637" s="2"/>
+      <c r="H637" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I637" s="2" t="s">
+        <v>2775</v>
+      </c>
+      <c r="J637" s="2" t="s">
+        <v>2776</v>
+      </c>
+      <c r="K637" s="2" t="s">
+        <v>2777</v>
+      </c>
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="2" t="n">
         <v>637</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>2457</v>
+        <v>2773</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>2459</v>
+        <v>2778</v>
       </c>
       <c r="D638" s="2" t="s">
         <v>61</v>
@@ -28524,13 +30281,17 @@
         <v>1</v>
       </c>
       <c r="G638" s="2" t="s">
-        <v>2460</v>
-      </c>
-      <c r="H638" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I638" s="2"/>
-      <c r="J638" s="2"/>
+        <v>2779</v>
+      </c>
+      <c r="H638" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I638" s="2" t="s">
+        <v>2780</v>
+      </c>
+      <c r="J638" s="2" t="s">
+        <v>2781</v>
+      </c>
       <c r="K638" s="2"/>
     </row>
     <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28538,10 +30299,10 @@
         <v>638</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>2457</v>
+        <v>2773</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>2461</v>
+        <v>2782</v>
       </c>
       <c r="D639" s="2" t="s">
         <v>13</v>
@@ -28553,22 +30314,28 @@
         <v>2</v>
       </c>
       <c r="G639" s="2"/>
-      <c r="H639" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I639" s="2"/>
-      <c r="J639" s="2"/>
-      <c r="K639" s="2"/>
+      <c r="H639" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I639" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J639" s="2" t="s">
+        <v>2783</v>
+      </c>
+      <c r="K639" s="2" t="s">
+        <v>2784</v>
+      </c>
     </row>
     <row r="640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="2" t="n">
         <v>639</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>2457</v>
+        <v>2773</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>2462</v>
+        <v>2785</v>
       </c>
       <c r="D640" s="2" t="s">
         <v>20</v>
@@ -28580,19 +30347,25 @@
         <v>1</v>
       </c>
       <c r="G640" s="2"/>
-      <c r="H640" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I640" s="2"/>
-      <c r="J640" s="2"/>
-      <c r="K640" s="2"/>
+      <c r="H640" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I640" s="2" t="s">
+        <v>2786</v>
+      </c>
+      <c r="J640" s="2" t="s">
+        <v>2787</v>
+      </c>
+      <c r="K640" s="2" t="s">
+        <v>2788</v>
+      </c>
     </row>
     <row r="641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="2" t="n">
         <v>640</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>2457</v>
+        <v>2773</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>1516</v>
@@ -28607,24 +30380,30 @@
         <v>1</v>
       </c>
       <c r="G641" s="2" t="s">
-        <v>2463</v>
-      </c>
-      <c r="H641" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I641" s="2"/>
-      <c r="J641" s="2"/>
-      <c r="K641" s="2"/>
+        <v>2789</v>
+      </c>
+      <c r="H641" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I641" s="2" t="s">
+        <v>2790</v>
+      </c>
+      <c r="J641" s="2" t="s">
+        <v>2791</v>
+      </c>
+      <c r="K641" s="2" t="s">
+        <v>2792</v>
+      </c>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="2" t="n">
         <v>641</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>2464</v>
+        <v>2793</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>2465</v>
+        <v>2794</v>
       </c>
       <c r="D642" s="2" t="s">
         <v>61</v>
@@ -28636,24 +30415,30 @@
         <v>1</v>
       </c>
       <c r="G642" s="2" t="s">
-        <v>2466</v>
-      </c>
-      <c r="H642" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I642" s="2"/>
-      <c r="J642" s="2"/>
-      <c r="K642" s="2"/>
+        <v>2795</v>
+      </c>
+      <c r="H642" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I642" s="2" t="s">
+        <v>2796</v>
+      </c>
+      <c r="J642" s="2" t="s">
+        <v>2797</v>
+      </c>
+      <c r="K642" s="2" t="s">
+        <v>2798</v>
+      </c>
     </row>
     <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A643" s="2" t="n">
         <v>642</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>2464</v>
+        <v>2793</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>2453</v>
+        <v>2763</v>
       </c>
       <c r="D643" s="2" t="s">
         <v>20</v>
@@ -28665,22 +30450,28 @@
         <v>1</v>
       </c>
       <c r="G643" s="2"/>
-      <c r="H643" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I643" s="2"/>
-      <c r="J643" s="2"/>
-      <c r="K643" s="2"/>
+      <c r="H643" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I643" s="2" t="s">
+        <v>2799</v>
+      </c>
+      <c r="J643" s="2" t="s">
+        <v>2800</v>
+      </c>
+      <c r="K643" s="2" t="s">
+        <v>2801</v>
+      </c>
     </row>
     <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A644" s="2" t="n">
         <v>643</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>2464</v>
+        <v>2793</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>2467</v>
+        <v>2802</v>
       </c>
       <c r="D644" s="2" t="s">
         <v>61</v>
@@ -28692,24 +30483,30 @@
         <v>3</v>
       </c>
       <c r="G644" s="2" t="s">
-        <v>2468</v>
-      </c>
-      <c r="H644" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I644" s="2"/>
-      <c r="J644" s="2"/>
-      <c r="K644" s="2"/>
+        <v>2803</v>
+      </c>
+      <c r="H644" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I644" s="2" t="s">
+        <v>2804</v>
+      </c>
+      <c r="J644" s="2" t="s">
+        <v>2805</v>
+      </c>
+      <c r="K644" s="2" t="s">
+        <v>2806</v>
+      </c>
     </row>
     <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="2" t="n">
         <v>644</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>2464</v>
+        <v>2793</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>2469</v>
+        <v>2807</v>
       </c>
       <c r="D645" s="2" t="s">
         <v>20</v>
@@ -28721,22 +30518,28 @@
         <v>1</v>
       </c>
       <c r="G645" s="2"/>
-      <c r="H645" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I645" s="2"/>
-      <c r="J645" s="2"/>
-      <c r="K645" s="2"/>
+      <c r="H645" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I645" s="2" t="s">
+        <v>2808</v>
+      </c>
+      <c r="J645" s="2" t="s">
+        <v>2809</v>
+      </c>
+      <c r="K645" s="2" t="s">
+        <v>2810</v>
+      </c>
     </row>
     <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="2" t="n">
         <v>645</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>2470</v>
+        <v>2811</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>2471</v>
+        <v>2812</v>
       </c>
       <c r="D646" s="2" t="s">
         <v>13</v>
@@ -28748,19 +30551,25 @@
         <v>2</v>
       </c>
       <c r="G646" s="2"/>
-      <c r="H646" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I646" s="2"/>
-      <c r="J646" s="2"/>
-      <c r="K646" s="2"/>
+      <c r="H646" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I646" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J646" s="2" t="s">
+        <v>2813</v>
+      </c>
+      <c r="K646" s="2" t="s">
+        <v>2814</v>
+      </c>
     </row>
     <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="2" t="n">
         <v>646</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>2472</v>
+        <v>2815</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>1204</v>
@@ -28775,19 +30584,25 @@
         <v>3</v>
       </c>
       <c r="G647" s="2"/>
-      <c r="H647" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I647" s="2"/>
-      <c r="J647" s="2"/>
-      <c r="K647" s="2"/>
+      <c r="H647" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I647" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J647" s="2" t="s">
+        <v>2816</v>
+      </c>
+      <c r="K647" s="2" t="s">
+        <v>2817</v>
+      </c>
     </row>
     <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="2" t="n">
         <v>647</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>2473</v>
+        <v>2818</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>1481</v>
@@ -28802,12 +30617,18 @@
         <v>2</v>
       </c>
       <c r="G648" s="2"/>
-      <c r="H648" s="6" t="s">
-        <v>2070</v>
-      </c>
-      <c r="I648" s="2"/>
-      <c r="J648" s="2"/>
-      <c r="K648" s="2"/>
+      <c r="H648" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I648" s="2" t="s">
+        <v>2819</v>
+      </c>
+      <c r="J648" s="2" t="s">
+        <v>2820</v>
+      </c>
+      <c r="K648" s="2" t="s">
+        <v>2821</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K648"/>
@@ -28834,97 +30655,97 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>2474</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2475</v>
+      <c r="A1" s="6" t="s">
+        <v>2822</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>2823</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="8" t="n">
+      <c r="A2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="7" t="n">
         <f aca="false">COUNTIF('Master list'!H2:H648,"Confirmed")</f>
-        <v>273</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7" t="n">
         <f aca="false">COUNTIF('Master list'!H2:H648,"Possible")</f>
-        <v>173</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="n">
         <f aca="false">COUNTIF('Master list'!H2:H648,"Negative")</f>
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>2070</v>
-      </c>
-      <c r="B5" s="8" t="n">
+      <c r="A5" s="7" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B5" s="7" t="n">
         <f aca="false">COUNTIF('Master list'!H2:H648,"Not yet checked")</f>
-        <v>139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>2476</v>
-      </c>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="7" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B6" s="7" t="n">
         <f aca="false">SUM(B2:B5)</f>
         <v>647</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>2477</v>
-      </c>
-      <c r="B8" s="8"/>
+      <c r="A8" s="7" t="s">
+        <v>2826</v>
+      </c>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>2478</v>
-      </c>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>2479</v>
-      </c>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>2480</v>
-      </c>
-      <c r="B11" s="8"/>
+      <c r="A11" s="7" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>2481</v>
-      </c>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7" t="s">
+        <v>2830</v>
+      </c>
+      <c r="B12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>2482</v>
-      </c>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B13" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
